--- a/data/intermediate/25-26/data_preprocess_merge.xlsx
+++ b/data/intermediate/25-26/data_preprocess_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z533"/>
+  <dimension ref="A1:AG533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,41 @@
           <t>Mf19_20</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>FVM24_25</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>FVM23_24</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>FVM22_23</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>FVM21_22</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>FVM20_21</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>FVM19_20</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>FVM18_19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -623,6 +658,19 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -705,6 +753,23 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>47</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -775,6 +840,19 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>69</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -833,6 +911,13 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -909,6 +994,21 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -979,6 +1079,19 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1061,6 +1174,23 @@
       <c r="Z8" t="n">
         <v>3.25</v>
       </c>
+      <c r="AA8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1125,6 +1255,17 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1189,6 +1330,17 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>111</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1253,6 +1405,17 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1340,6 +1503,27 @@
       </c>
       <c r="Z12" t="n">
         <v>4.29</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1399,6 +1583,15 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1481,6 +1674,23 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1569,6 +1779,27 @@
       <c r="Z15" t="n">
         <v>4.31</v>
       </c>
+      <c r="AA15" t="n">
+        <v>53</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1651,6 +1882,25 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1709,6 +1959,15 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1761,6 +2020,13 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1813,6 +2079,13 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1877,6 +2150,17 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1935,6 +2219,15 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1999,6 +2292,17 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2087,6 +2391,27 @@
       <c r="Z23" t="n">
         <v>4.29</v>
       </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2174,6 +2499,27 @@
       </c>
       <c r="Z24" t="n">
         <v>4.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2257,6 +2603,21 @@
       <c r="Z25" t="n">
         <v>4.25</v>
       </c>
+      <c r="AA25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2315,6 +2676,17 @@
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2367,6 +2739,13 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2431,6 +2810,17 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2483,6 +2873,13 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2559,6 +2956,21 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2617,6 +3029,15 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2681,6 +3102,17 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2769,6 +3201,27 @@
       <c r="Z33" t="n">
         <v>5</v>
       </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2856,6 +3309,27 @@
       </c>
       <c r="Z34" t="n">
         <v>5.33</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2927,6 +3401,19 @@
       <c r="Z35" t="n">
         <v>0</v>
       </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2991,6 +3478,17 @@
       <c r="Z36" t="n">
         <v>4</v>
       </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3055,6 +3553,17 @@
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3113,6 +3622,13 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3177,6 +3693,17 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3241,6 +3768,17 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3328,6 +3866,27 @@
       </c>
       <c r="Z41" t="n">
         <v>6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3387,6 +3946,15 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3451,6 +4019,17 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3538,6 +4117,27 @@
       </c>
       <c r="Z44" t="n">
         <v>5.64</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3597,6 +4197,15 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3679,6 +4288,19 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3743,6 +4365,15 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3807,6 +4438,17 @@
       <c r="Z48" t="n">
         <v>0</v>
       </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3889,6 +4531,19 @@
       <c r="Z49" t="n">
         <v>0</v>
       </c>
+      <c r="AA49" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3941,6 +4596,13 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4022,6 +4684,25 @@
       </c>
       <c r="Z51" t="n">
         <v>4.83</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4091,6 +4772,17 @@
         <v>0</v>
       </c>
       <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4145,6 +4837,13 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4232,6 +4931,27 @@
       </c>
       <c r="Z54" t="n">
         <v>4</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4291,6 +5011,15 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4361,6 +5090,19 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4413,6 +5155,13 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4471,6 +5220,15 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4559,6 +5317,23 @@
       <c r="Z59" t="n">
         <v>4.94</v>
       </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4611,6 +5386,13 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4663,6 +5445,13 @@
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4715,6 +5504,13 @@
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4773,6 +5569,13 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4825,6 +5628,13 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4883,6 +5693,15 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4935,6 +5754,13 @@
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4987,6 +5813,13 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5039,6 +5872,13 @@
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5127,6 +5967,27 @@
       <c r="Z69" t="n">
         <v>5.94</v>
       </c>
+      <c r="AA69" t="n">
+        <v>101</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>150</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5214,6 +6075,27 @@
       </c>
       <c r="Z70" t="n">
         <v>6</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>57</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>55</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -5273,6 +6155,15 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5331,6 +6222,13 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5389,6 +6287,15 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5476,6 +6383,27 @@
       </c>
       <c r="Z74" t="n">
         <v>6.43</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -5553,6 +6481,21 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5617,6 +6560,17 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5704,6 +6658,27 @@
       </c>
       <c r="Z77" t="n">
         <v>5.88</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5775,6 +6750,19 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5857,6 +6845,23 @@
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5927,6 +6932,19 @@
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5979,6 +6997,13 @@
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6037,6 +7062,13 @@
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6124,6 +7156,27 @@
       </c>
       <c r="Z83" t="n">
         <v>6.04</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6183,6 +7236,13 @@
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6241,6 +7301,13 @@
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6293,6 +7360,13 @@
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6381,6 +7455,25 @@
       <c r="Z87" t="n">
         <v>5.83</v>
       </c>
+      <c r="AA87" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6457,6 +7550,21 @@
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6521,6 +7629,17 @@
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6608,6 +7727,25 @@
       </c>
       <c r="Z90" t="n">
         <v>7.38</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -6685,6 +7823,21 @@
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6743,6 +7896,13 @@
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6831,6 +7991,25 @@
       <c r="Z93" t="n">
         <v>5.9</v>
       </c>
+      <c r="AA93" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6901,6 +8080,19 @@
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6965,6 +8157,17 @@
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7017,6 +8220,13 @@
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7093,6 +8303,19 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7151,6 +8374,15 @@
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7233,6 +8465,23 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7291,6 +8540,13 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7361,6 +8617,19 @@
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7425,6 +8694,17 @@
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7495,6 +8775,19 @@
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7553,6 +8846,13 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7629,6 +8929,19 @@
       <c r="Z105" t="n">
         <v>0</v>
       </c>
+      <c r="AA105" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7693,6 +9006,15 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7757,6 +9079,17 @@
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7844,6 +9177,27 @@
       </c>
       <c r="Z108" t="n">
         <v>6.17</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>67</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7903,6 +9257,15 @@
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7967,6 +9330,17 @@
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8019,6 +9393,13 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8071,6 +9452,13 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8123,6 +9511,13 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8175,6 +9570,13 @@
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8239,6 +9641,17 @@
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8297,6 +9710,15 @@
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8373,6 +9795,21 @@
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8443,6 +9880,19 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8495,6 +9945,13 @@
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8553,6 +10010,15 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8605,6 +10071,13 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8692,6 +10165,27 @@
       </c>
       <c r="Z122" t="n">
         <v>5.5</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -8769,6 +10263,21 @@
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8839,6 +10348,19 @@
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8927,6 +10449,27 @@
       <c r="Z125" t="n">
         <v>6.14</v>
       </c>
+      <c r="AA125" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9015,6 +10558,27 @@
       <c r="Z126" t="n">
         <v>6.54</v>
       </c>
+      <c r="AA126" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9097,6 +10661,23 @@
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
+      <c r="AA127" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9185,6 +10766,23 @@
       <c r="Z128" t="n">
         <v>0</v>
       </c>
+      <c r="AA128" t="n">
+        <v>57</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9243,6 +10841,15 @@
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9295,6 +10902,13 @@
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9353,6 +10967,15 @@
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9411,6 +11034,15 @@
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9469,6 +11101,15 @@
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9521,6 +11162,13 @@
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9573,6 +11221,13 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9660,6 +11315,27 @@
       </c>
       <c r="Z136" t="n">
         <v>6.21</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -9725,6 +11401,17 @@
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -9795,6 +11482,19 @@
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
+      <c r="AA138" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9865,6 +11565,19 @@
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -9923,6 +11636,15 @@
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -9981,6 +11703,15 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr"/>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10039,6 +11770,13 @@
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10109,6 +11847,19 @@
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10173,6 +11924,17 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10237,6 +11999,17 @@
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10307,6 +12080,19 @@
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10365,6 +12151,15 @@
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10435,6 +12230,19 @@
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10493,6 +12301,15 @@
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr"/>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10581,6 +12398,23 @@
       <c r="Z150" t="n">
         <v>6</v>
       </c>
+      <c r="AA150" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10657,6 +12491,21 @@
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10715,6 +12564,13 @@
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10773,6 +12629,15 @@
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10855,6 +12720,21 @@
       <c r="Z154" t="n">
         <v>5.17</v>
       </c>
+      <c r="AA154" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -10931,6 +12811,21 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="inlineStr"/>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -11007,6 +12902,21 @@
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11077,6 +12987,19 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -11129,6 +13052,13 @@
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
       <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -11187,6 +13117,15 @@
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr"/>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11263,6 +13202,21 @@
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="inlineStr"/>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11315,6 +13269,13 @@
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr"/>
       <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11397,6 +13358,23 @@
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11461,6 +13439,17 @@
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11531,6 +13520,19 @@
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr"/>
       <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11583,6 +13585,13 @@
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr"/>
       <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11635,6 +13644,13 @@
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr"/>
       <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11687,6 +13703,13 @@
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr"/>
       <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11751,6 +13774,17 @@
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11809,6 +13843,15 @@
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11861,6 +13904,13 @@
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr"/>
       <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11931,6 +13981,19 @@
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr"/>
       <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="inlineStr"/>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -12018,6 +14081,27 @@
       </c>
       <c r="Z172" t="n">
         <v>6.43</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -12089,6 +14173,19 @@
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr"/>
       <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="inlineStr"/>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -12176,6 +14273,27 @@
       </c>
       <c r="Z174" t="n">
         <v>6.04</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -12235,6 +14353,13 @@
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12323,6 +14448,25 @@
       <c r="Z176" t="n">
         <v>5.78</v>
       </c>
+      <c r="AA176" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -12393,6 +14537,19 @@
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="inlineStr"/>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12457,6 +14614,17 @@
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="inlineStr"/>
+      <c r="AA178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
+      <c r="AE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12509,6 +14677,13 @@
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
+      <c r="AE179" t="inlineStr"/>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12597,6 +14772,25 @@
       <c r="Z180" t="n">
         <v>5.61</v>
       </c>
+      <c r="AA180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12661,6 +14855,15 @@
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="inlineStr"/>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="inlineStr"/>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12731,6 +14934,19 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr"/>
+      <c r="AA182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD182" t="inlineStr"/>
+      <c r="AE182" t="inlineStr"/>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12818,6 +15034,27 @@
       </c>
       <c r="Z183" t="n">
         <v>6.18</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -12877,6 +15114,13 @@
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12929,6 +15173,13 @@
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12981,6 +15232,13 @@
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -13039,6 +15297,13 @@
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="inlineStr"/>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -13091,6 +15356,13 @@
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="inlineStr"/>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -13149,6 +15421,15 @@
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr"/>
       <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -13201,6 +15482,13 @@
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr"/>
       <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="inlineStr"/>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -13288,6 +15576,27 @@
       </c>
       <c r="Z191" t="n">
         <v>5.66</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -13353,6 +15662,17 @@
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr"/>
       <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr"/>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -13440,6 +15760,27 @@
       </c>
       <c r="Z193" t="n">
         <v>4.67</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -13517,6 +15858,21 @@
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr"/>
       <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="inlineStr"/>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -13581,6 +15937,17 @@
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr"/>
       <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr"/>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -13663,6 +16030,19 @@
       <c r="Z196" t="n">
         <v>5.83</v>
       </c>
+      <c r="AA196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -13721,6 +16101,13 @@
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -13773,6 +16160,13 @@
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr"/>
       <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -13825,6 +16219,13 @@
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr"/>
       <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -13877,6 +16278,13 @@
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -13935,6 +16343,15 @@
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -14022,6 +16439,27 @@
       </c>
       <c r="Z202" t="n">
         <v>5.73</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -14099,6 +16537,19 @@
       <c r="Z203" t="n">
         <v>5.85</v>
       </c>
+      <c r="AA203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr"/>
+      <c r="AF203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -14187,6 +16638,27 @@
       <c r="Z204" t="n">
         <v>6.6</v>
       </c>
+      <c r="AA204" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -14275,6 +16747,25 @@
       <c r="Z205" t="n">
         <v>5.95</v>
       </c>
+      <c r="AA205" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -14363,6 +16854,27 @@
       <c r="Z206" t="n">
         <v>5.74</v>
       </c>
+      <c r="AA206" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -14450,6 +16962,27 @@
       </c>
       <c r="Z207" t="n">
         <v>6.16</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -14509,6 +17042,15 @@
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr"/>
       <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -14583,6 +17125,17 @@
         <v>0</v>
       </c>
       <c r="Z209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14649,6 +17202,17 @@
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr"/>
       <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr"/>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -14707,6 +17271,13 @@
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr"/>
       <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -14759,6 +17330,13 @@
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr"/>
       <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -14811,6 +17389,13 @@
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr"/>
       <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr"/>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -14863,6 +17448,13 @@
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="inlineStr"/>
       <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -14933,6 +17525,17 @@
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="inlineStr"/>
       <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -14985,6 +17588,13 @@
       <c r="X216" t="inlineStr"/>
       <c r="Y216" t="inlineStr"/>
       <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -15072,6 +17682,27 @@
       </c>
       <c r="Z217" t="n">
         <v>5.68</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -15125,6 +17756,13 @@
       <c r="X218" t="inlineStr"/>
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -15183,6 +17821,13 @@
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="inlineStr"/>
       <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+      <c r="AE219" t="inlineStr"/>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -15270,6 +17915,25 @@
       </c>
       <c r="Z220" t="n">
         <v>5.19</v>
+      </c>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -15329,6 +17993,15 @@
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="inlineStr"/>
       <c r="Z221" t="inlineStr"/>
+      <c r="AA221" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
+      <c r="AE221" t="inlineStr"/>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -15387,6 +18060,15 @@
       <c r="X222" t="inlineStr"/>
       <c r="Y222" t="inlineStr"/>
       <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
+      <c r="AE222" t="inlineStr"/>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -15439,6 +18121,13 @@
       <c r="X223" t="inlineStr"/>
       <c r="Y223" t="inlineStr"/>
       <c r="Z223" t="inlineStr"/>
+      <c r="AA223" t="inlineStr"/>
+      <c r="AB223" t="inlineStr"/>
+      <c r="AC223" t="inlineStr"/>
+      <c r="AD223" t="inlineStr"/>
+      <c r="AE223" t="inlineStr"/>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -15526,6 +18215,27 @@
       </c>
       <c r="Z224" t="n">
         <v>6.43</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -15585,6 +18295,13 @@
       <c r="X225" t="inlineStr"/>
       <c r="Y225" t="inlineStr"/>
       <c r="Z225" t="inlineStr"/>
+      <c r="AA225" t="inlineStr"/>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr"/>
+      <c r="AE225" t="inlineStr"/>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -15637,6 +18354,13 @@
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="inlineStr"/>
       <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="inlineStr"/>
+      <c r="AD226" t="inlineStr"/>
+      <c r="AE226" t="inlineStr"/>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -15689,6 +18413,13 @@
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr"/>
       <c r="Z227" t="inlineStr"/>
+      <c r="AA227" t="inlineStr"/>
+      <c r="AB227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr"/>
+      <c r="AE227" t="inlineStr"/>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -15741,6 +18472,13 @@
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr"/>
       <c r="Z228" t="inlineStr"/>
+      <c r="AA228" t="inlineStr"/>
+      <c r="AB228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr"/>
+      <c r="AD228" t="inlineStr"/>
+      <c r="AE228" t="inlineStr"/>
+      <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -15793,6 +18531,13 @@
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr"/>
       <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
+      <c r="AE229" t="inlineStr"/>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -15845,6 +18590,13 @@
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr"/>
       <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
+      <c r="AB230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
+      <c r="AE230" t="inlineStr"/>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -15897,6 +18649,13 @@
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="inlineStr"/>
       <c r="Z231" t="inlineStr"/>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr"/>
+      <c r="AD231" t="inlineStr"/>
+      <c r="AE231" t="inlineStr"/>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -15972,6 +18731,19 @@
       </c>
       <c r="Z232" t="n">
         <v>5.83</v>
+      </c>
+      <c r="AA232" t="inlineStr"/>
+      <c r="AB232" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr"/>
+      <c r="AE232" t="inlineStr"/>
+      <c r="AF232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -16025,6 +18797,13 @@
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr"/>
       <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
+      <c r="AD233" t="inlineStr"/>
+      <c r="AE233" t="inlineStr"/>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -16077,6 +18856,13 @@
       <c r="X234" t="inlineStr"/>
       <c r="Y234" t="inlineStr"/>
       <c r="Z234" t="inlineStr"/>
+      <c r="AA234" t="inlineStr"/>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr"/>
+      <c r="AD234" t="inlineStr"/>
+      <c r="AE234" t="inlineStr"/>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -16153,6 +18939,21 @@
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="inlineStr"/>
       <c r="Z235" t="inlineStr"/>
+      <c r="AA235" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="inlineStr"/>
+      <c r="AF235" t="inlineStr"/>
+      <c r="AG235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -16235,6 +19036,23 @@
       <c r="Z236" t="n">
         <v>5.68</v>
       </c>
+      <c r="AA236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -16322,6 +19140,23 @@
       </c>
       <c r="Z237" t="n">
         <v>5.7</v>
+      </c>
+      <c r="AA237" t="inlineStr"/>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -16381,6 +19216,15 @@
       <c r="X238" t="inlineStr"/>
       <c r="Y238" t="inlineStr"/>
       <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB238" t="inlineStr"/>
+      <c r="AC238" t="inlineStr"/>
+      <c r="AD238" t="inlineStr"/>
+      <c r="AE238" t="inlineStr"/>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -16468,6 +19312,27 @@
       </c>
       <c r="Z239" t="n">
         <v>6.05</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -16521,6 +19386,13 @@
       <c r="X240" t="inlineStr"/>
       <c r="Y240" t="inlineStr"/>
       <c r="Z240" t="inlineStr"/>
+      <c r="AA240" t="inlineStr"/>
+      <c r="AB240" t="inlineStr"/>
+      <c r="AC240" t="inlineStr"/>
+      <c r="AD240" t="inlineStr"/>
+      <c r="AE240" t="inlineStr"/>
+      <c r="AF240" t="inlineStr"/>
+      <c r="AG240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -16573,6 +19445,13 @@
       <c r="X241" t="inlineStr"/>
       <c r="Y241" t="inlineStr"/>
       <c r="Z241" t="inlineStr"/>
+      <c r="AA241" t="inlineStr"/>
+      <c r="AB241" t="inlineStr"/>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
+      <c r="AE241" t="inlineStr"/>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -16625,6 +19504,13 @@
       <c r="X242" t="inlineStr"/>
       <c r="Y242" t="inlineStr"/>
       <c r="Z242" t="inlineStr"/>
+      <c r="AA242" t="inlineStr"/>
+      <c r="AB242" t="inlineStr"/>
+      <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
+      <c r="AE242" t="inlineStr"/>
+      <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -16700,6 +19586,23 @@
       </c>
       <c r="Z243" t="n">
         <v>5.83</v>
+      </c>
+      <c r="AA243" t="inlineStr"/>
+      <c r="AB243" t="inlineStr"/>
+      <c r="AC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -16753,6 +19656,13 @@
       <c r="X244" t="inlineStr"/>
       <c r="Y244" t="inlineStr"/>
       <c r="Z244" t="inlineStr"/>
+      <c r="AA244" t="inlineStr"/>
+      <c r="AB244" t="inlineStr"/>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
+      <c r="AE244" t="inlineStr"/>
+      <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -16805,6 +19715,13 @@
       <c r="X245" t="inlineStr"/>
       <c r="Y245" t="inlineStr"/>
       <c r="Z245" t="inlineStr"/>
+      <c r="AA245" t="inlineStr"/>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
+      <c r="AE245" t="inlineStr"/>
+      <c r="AF245" t="inlineStr"/>
+      <c r="AG245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -16863,6 +19780,13 @@
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="inlineStr"/>
       <c r="Z246" t="inlineStr"/>
+      <c r="AA246" t="inlineStr"/>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
+      <c r="AE246" t="inlineStr"/>
+      <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -16915,6 +19839,13 @@
       <c r="X247" t="inlineStr"/>
       <c r="Y247" t="inlineStr"/>
       <c r="Z247" t="inlineStr"/>
+      <c r="AA247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr"/>
+      <c r="AE247" t="inlineStr"/>
+      <c r="AF247" t="inlineStr"/>
+      <c r="AG247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -16967,6 +19898,13 @@
       <c r="X248" t="inlineStr"/>
       <c r="Y248" t="inlineStr"/>
       <c r="Z248" t="inlineStr"/>
+      <c r="AA248" t="inlineStr"/>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr"/>
+      <c r="AE248" t="inlineStr"/>
+      <c r="AF248" t="inlineStr"/>
+      <c r="AG248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -17019,6 +19957,13 @@
       <c r="X249" t="inlineStr"/>
       <c r="Y249" t="inlineStr"/>
       <c r="Z249" t="inlineStr"/>
+      <c r="AA249" t="inlineStr"/>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
+      <c r="AE249" t="inlineStr"/>
+      <c r="AF249" t="inlineStr"/>
+      <c r="AG249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -17071,6 +20016,15 @@
       <c r="X250" t="inlineStr"/>
       <c r="Y250" t="inlineStr"/>
       <c r="Z250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr"/>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+      <c r="AE250" t="inlineStr"/>
+      <c r="AF250" t="inlineStr"/>
+      <c r="AG250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -17123,6 +20077,13 @@
       <c r="X251" t="inlineStr"/>
       <c r="Y251" t="inlineStr"/>
       <c r="Z251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr"/>
+      <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
+      <c r="AE251" t="inlineStr"/>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -17175,6 +20136,13 @@
       <c r="X252" t="inlineStr"/>
       <c r="Y252" t="inlineStr"/>
       <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
+      <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+      <c r="AE252" t="inlineStr"/>
+      <c r="AF252" t="inlineStr"/>
+      <c r="AG252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -17233,6 +20201,15 @@
       <c r="X253" t="inlineStr"/>
       <c r="Y253" t="inlineStr"/>
       <c r="Z253" t="inlineStr"/>
+      <c r="AA253" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr"/>
+      <c r="AE253" t="inlineStr"/>
+      <c r="AF253" t="inlineStr"/>
+      <c r="AG253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -17291,6 +20268,15 @@
       <c r="X254" t="inlineStr"/>
       <c r="Y254" t="inlineStr"/>
       <c r="Z254" t="inlineStr"/>
+      <c r="AA254" t="n">
+        <v>57</v>
+      </c>
+      <c r="AB254" t="inlineStr"/>
+      <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
+      <c r="AE254" t="inlineStr"/>
+      <c r="AF254" t="inlineStr"/>
+      <c r="AG254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -17343,6 +20329,13 @@
       <c r="X255" t="inlineStr"/>
       <c r="Y255" t="inlineStr"/>
       <c r="Z255" t="inlineStr"/>
+      <c r="AA255" t="inlineStr"/>
+      <c r="AB255" t="inlineStr"/>
+      <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
+      <c r="AE255" t="inlineStr"/>
+      <c r="AF255" t="inlineStr"/>
+      <c r="AG255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -17430,6 +20423,27 @@
       </c>
       <c r="Z256" t="n">
         <v>7.24</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>163</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>330</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -17495,6 +20509,17 @@
       <c r="X257" t="inlineStr"/>
       <c r="Y257" t="inlineStr"/>
       <c r="Z257" t="inlineStr"/>
+      <c r="AA257" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>300</v>
+      </c>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
+      <c r="AE257" t="inlineStr"/>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -17577,6 +20602,23 @@
       <c r="Z258" t="n">
         <v>5.93</v>
       </c>
+      <c r="AA258" t="inlineStr"/>
+      <c r="AB258" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -17629,6 +20671,13 @@
       <c r="X259" t="inlineStr"/>
       <c r="Y259" t="inlineStr"/>
       <c r="Z259" t="inlineStr"/>
+      <c r="AA259" t="inlineStr"/>
+      <c r="AB259" t="inlineStr"/>
+      <c r="AC259" t="inlineStr"/>
+      <c r="AD259" t="inlineStr"/>
+      <c r="AE259" t="inlineStr"/>
+      <c r="AF259" t="inlineStr"/>
+      <c r="AG259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -17687,6 +20736,15 @@
       <c r="X260" t="inlineStr"/>
       <c r="Y260" t="inlineStr"/>
       <c r="Z260" t="inlineStr"/>
+      <c r="AA260" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB260" t="inlineStr"/>
+      <c r="AC260" t="inlineStr"/>
+      <c r="AD260" t="inlineStr"/>
+      <c r="AE260" t="inlineStr"/>
+      <c r="AF260" t="inlineStr"/>
+      <c r="AG260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -17774,6 +20832,27 @@
       </c>
       <c r="Z261" t="n">
         <v>6.18</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -17833,6 +20912,15 @@
       <c r="X262" t="inlineStr"/>
       <c r="Y262" t="inlineStr"/>
       <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr"/>
+      <c r="AE262" t="inlineStr"/>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -17920,6 +21008,27 @@
       </c>
       <c r="Z263" t="n">
         <v>6.69</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>200</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>92</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -18003,6 +21112,23 @@
       <c r="Z264" t="n">
         <v>6.8</v>
       </c>
+      <c r="AA264" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr"/>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -18091,6 +21217,27 @@
       <c r="Z265" t="n">
         <v>6.09</v>
       </c>
+      <c r="AA265" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>57</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>73</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -18173,6 +21320,21 @@
       <c r="X266" t="inlineStr"/>
       <c r="Y266" t="inlineStr"/>
       <c r="Z266" t="inlineStr"/>
+      <c r="AA266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC266" t="inlineStr"/>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF266" t="inlineStr"/>
+      <c r="AG266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -18231,6 +21393,15 @@
       <c r="X267" t="inlineStr"/>
       <c r="Y267" t="inlineStr"/>
       <c r="Z267" t="inlineStr"/>
+      <c r="AA267" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB267" t="inlineStr"/>
+      <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr"/>
+      <c r="AE267" t="inlineStr"/>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -18283,6 +21454,13 @@
       <c r="X268" t="inlineStr"/>
       <c r="Y268" t="inlineStr"/>
       <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr"/>
+      <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr"/>
+      <c r="AE268" t="inlineStr"/>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -18370,6 +21548,27 @@
       </c>
       <c r="Z269" t="n">
         <v>5.84</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -18423,6 +21622,13 @@
       <c r="X270" t="inlineStr"/>
       <c r="Y270" t="inlineStr"/>
       <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
+      <c r="AB270" t="inlineStr"/>
+      <c r="AC270" t="inlineStr"/>
+      <c r="AD270" t="inlineStr"/>
+      <c r="AE270" t="inlineStr"/>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -18493,6 +21699,19 @@
       <c r="X271" t="inlineStr"/>
       <c r="Y271" t="inlineStr"/>
       <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD271" t="inlineStr"/>
+      <c r="AE271" t="inlineStr"/>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -18551,6 +21770,15 @@
       <c r="X272" t="inlineStr"/>
       <c r="Y272" t="inlineStr"/>
       <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB272" t="inlineStr"/>
+      <c r="AC272" t="inlineStr"/>
+      <c r="AD272" t="inlineStr"/>
+      <c r="AE272" t="inlineStr"/>
+      <c r="AF272" t="inlineStr"/>
+      <c r="AG272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -18633,6 +21861,23 @@
       <c r="X273" t="inlineStr"/>
       <c r="Y273" t="inlineStr"/>
       <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -18697,6 +21942,17 @@
       <c r="X274" t="inlineStr"/>
       <c r="Y274" t="inlineStr"/>
       <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC274" t="inlineStr"/>
+      <c r="AD274" t="inlineStr"/>
+      <c r="AE274" t="inlineStr"/>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -18785,6 +22041,23 @@
       <c r="Z275" t="n">
         <v>6.91</v>
       </c>
+      <c r="AA275" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC275" t="inlineStr"/>
+      <c r="AD275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -18873,6 +22146,25 @@
       <c r="Z276" t="n">
         <v>6.08</v>
       </c>
+      <c r="AA276" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -18949,6 +22241,21 @@
       <c r="X277" t="inlineStr"/>
       <c r="Y277" t="inlineStr"/>
       <c r="Z277" t="inlineStr"/>
+      <c r="AA277" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="inlineStr"/>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -19007,6 +22314,15 @@
       <c r="X278" t="inlineStr"/>
       <c r="Y278" t="inlineStr"/>
       <c r="Z278" t="inlineStr"/>
+      <c r="AA278" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB278" t="inlineStr"/>
+      <c r="AC278" t="inlineStr"/>
+      <c r="AD278" t="inlineStr"/>
+      <c r="AE278" t="inlineStr"/>
+      <c r="AF278" t="inlineStr"/>
+      <c r="AG278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -19071,6 +22387,17 @@
       <c r="X279" t="inlineStr"/>
       <c r="Y279" t="inlineStr"/>
       <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
+      <c r="AB279" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD279" t="inlineStr"/>
+      <c r="AE279" t="inlineStr"/>
+      <c r="AF279" t="inlineStr"/>
+      <c r="AG279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -19123,6 +22450,13 @@
       <c r="X280" t="inlineStr"/>
       <c r="Y280" t="inlineStr"/>
       <c r="Z280" t="inlineStr"/>
+      <c r="AA280" t="inlineStr"/>
+      <c r="AB280" t="inlineStr"/>
+      <c r="AC280" t="inlineStr"/>
+      <c r="AD280" t="inlineStr"/>
+      <c r="AE280" t="inlineStr"/>
+      <c r="AF280" t="inlineStr"/>
+      <c r="AG280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -19205,6 +22539,23 @@
       <c r="X281" t="inlineStr"/>
       <c r="Y281" t="inlineStr"/>
       <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -19293,6 +22644,25 @@
       <c r="Z282" t="n">
         <v>7.59</v>
       </c>
+      <c r="AA282" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -19351,6 +22721,15 @@
       <c r="X283" t="inlineStr"/>
       <c r="Y283" t="inlineStr"/>
       <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB283" t="inlineStr"/>
+      <c r="AC283" t="inlineStr"/>
+      <c r="AD283" t="inlineStr"/>
+      <c r="AE283" t="inlineStr"/>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -19415,6 +22794,17 @@
       <c r="X284" t="inlineStr"/>
       <c r="Y284" t="inlineStr"/>
       <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC284" t="inlineStr"/>
+      <c r="AD284" t="inlineStr"/>
+      <c r="AE284" t="inlineStr"/>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -19473,6 +22863,15 @@
       <c r="X285" t="inlineStr"/>
       <c r="Y285" t="inlineStr"/>
       <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB285" t="inlineStr"/>
+      <c r="AC285" t="inlineStr"/>
+      <c r="AD285" t="inlineStr"/>
+      <c r="AE285" t="inlineStr"/>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -19525,6 +22924,13 @@
       <c r="X286" t="inlineStr"/>
       <c r="Y286" t="inlineStr"/>
       <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
+      <c r="AB286" t="inlineStr"/>
+      <c r="AC286" t="inlineStr"/>
+      <c r="AD286" t="inlineStr"/>
+      <c r="AE286" t="inlineStr"/>
+      <c r="AF286" t="inlineStr"/>
+      <c r="AG286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -19601,6 +23007,21 @@
       <c r="X287" t="inlineStr"/>
       <c r="Y287" t="inlineStr"/>
       <c r="Z287" t="inlineStr"/>
+      <c r="AA287" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="inlineStr"/>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -19670,6 +23091,21 @@
       </c>
       <c r="Z288" t="n">
         <v>5.56</v>
+      </c>
+      <c r="AA288" t="inlineStr"/>
+      <c r="AB288" t="inlineStr"/>
+      <c r="AC288" t="inlineStr"/>
+      <c r="AD288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -19735,6 +23171,19 @@
       <c r="X289" t="inlineStr"/>
       <c r="Y289" t="inlineStr"/>
       <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC289" t="inlineStr"/>
+      <c r="AD289" t="inlineStr"/>
+      <c r="AE289" t="inlineStr"/>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -19811,6 +23260,19 @@
       <c r="Z290" t="n">
         <v>0</v>
       </c>
+      <c r="AA290" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD290" t="inlineStr"/>
+      <c r="AE290" t="inlineStr"/>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -19869,6 +23331,13 @@
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="inlineStr"/>
       <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
+      <c r="AB291" t="inlineStr"/>
+      <c r="AC291" t="inlineStr"/>
+      <c r="AD291" t="inlineStr"/>
+      <c r="AE291" t="inlineStr"/>
+      <c r="AF291" t="inlineStr"/>
+      <c r="AG291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -19945,6 +23414,19 @@
       <c r="Z292" t="n">
         <v>5.92</v>
       </c>
+      <c r="AA292" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB292" t="inlineStr"/>
+      <c r="AC292" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD292" t="inlineStr"/>
+      <c r="AE292" t="inlineStr"/>
+      <c r="AF292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -20015,6 +23497,19 @@
       <c r="X293" t="inlineStr"/>
       <c r="Y293" t="inlineStr"/>
       <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>330</v>
+      </c>
+      <c r="AC293" t="inlineStr"/>
+      <c r="AD293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE293" t="inlineStr"/>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -20103,6 +23598,25 @@
       <c r="Z294" t="n">
         <v>6.36</v>
       </c>
+      <c r="AA294" t="n">
+        <v>155</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>180</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -20179,6 +23693,21 @@
       <c r="X295" t="inlineStr"/>
       <c r="Y295" t="inlineStr"/>
       <c r="Z295" t="inlineStr"/>
+      <c r="AA295" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE295" t="inlineStr"/>
+      <c r="AF295" t="inlineStr"/>
+      <c r="AG295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -20267,6 +23796,27 @@
       <c r="Z296" t="n">
         <v>6.27</v>
       </c>
+      <c r="AA296" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -20354,6 +23904,27 @@
       </c>
       <c r="Z297" t="n">
         <v>5.81</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -20413,6 +23984,15 @@
       <c r="X298" t="inlineStr"/>
       <c r="Y298" t="inlineStr"/>
       <c r="Z298" t="inlineStr"/>
+      <c r="AA298" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB298" t="inlineStr"/>
+      <c r="AC298" t="inlineStr"/>
+      <c r="AD298" t="inlineStr"/>
+      <c r="AE298" t="inlineStr"/>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -20500,6 +24080,27 @@
       </c>
       <c r="Z299" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>175</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>64</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -20571,6 +24172,19 @@
       <c r="X300" t="inlineStr"/>
       <c r="Y300" t="inlineStr"/>
       <c r="Z300" t="inlineStr"/>
+      <c r="AA300" t="inlineStr"/>
+      <c r="AB300" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE300" t="inlineStr"/>
+      <c r="AF300" t="inlineStr"/>
+      <c r="AG300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -20635,6 +24249,13 @@
       <c r="X301" t="inlineStr"/>
       <c r="Y301" t="inlineStr"/>
       <c r="Z301" t="inlineStr"/>
+      <c r="AA301" t="inlineStr"/>
+      <c r="AB301" t="inlineStr"/>
+      <c r="AC301" t="inlineStr"/>
+      <c r="AD301" t="inlineStr"/>
+      <c r="AE301" t="inlineStr"/>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -20722,6 +24343,27 @@
       </c>
       <c r="Z302" t="n">
         <v>6.88</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>52</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>130</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -20805,6 +24447,23 @@
       <c r="Z303" t="n">
         <v>5.63</v>
       </c>
+      <c r="AA303" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC303" t="inlineStr"/>
+      <c r="AD303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -20892,6 +24551,27 @@
       </c>
       <c r="Z304" t="n">
         <v>6.17</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -20945,6 +24625,13 @@
       <c r="X305" t="inlineStr"/>
       <c r="Y305" t="inlineStr"/>
       <c r="Z305" t="inlineStr"/>
+      <c r="AA305" t="inlineStr"/>
+      <c r="AB305" t="inlineStr"/>
+      <c r="AC305" t="inlineStr"/>
+      <c r="AD305" t="inlineStr"/>
+      <c r="AE305" t="inlineStr"/>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -20997,6 +24684,13 @@
       <c r="X306" t="inlineStr"/>
       <c r="Y306" t="inlineStr"/>
       <c r="Z306" t="inlineStr"/>
+      <c r="AA306" t="inlineStr"/>
+      <c r="AB306" t="inlineStr"/>
+      <c r="AC306" t="inlineStr"/>
+      <c r="AD306" t="inlineStr"/>
+      <c r="AE306" t="inlineStr"/>
+      <c r="AF306" t="inlineStr"/>
+      <c r="AG306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -21085,6 +24779,23 @@
       <c r="Z307" t="n">
         <v>0</v>
       </c>
+      <c r="AA307" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD307" t="inlineStr"/>
+      <c r="AE307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -21137,6 +24848,13 @@
       <c r="X308" t="inlineStr"/>
       <c r="Y308" t="inlineStr"/>
       <c r="Z308" t="inlineStr"/>
+      <c r="AA308" t="inlineStr"/>
+      <c r="AB308" t="inlineStr"/>
+      <c r="AC308" t="inlineStr"/>
+      <c r="AD308" t="inlineStr"/>
+      <c r="AE308" t="inlineStr"/>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -21224,6 +24942,27 @@
       </c>
       <c r="Z309" t="n">
         <v>6.22</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -21301,6 +25040,19 @@
       <c r="X310" t="inlineStr"/>
       <c r="Y310" t="inlineStr"/>
       <c r="Z310" t="inlineStr"/>
+      <c r="AA310" t="inlineStr"/>
+      <c r="AB310" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE310" t="inlineStr"/>
+      <c r="AF310" t="inlineStr"/>
+      <c r="AG310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -21377,6 +25129,21 @@
       <c r="X311" t="inlineStr"/>
       <c r="Y311" t="inlineStr"/>
       <c r="Z311" t="inlineStr"/>
+      <c r="AA311" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>37</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE311" t="inlineStr"/>
+      <c r="AF311" t="inlineStr"/>
+      <c r="AG311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -21435,6 +25202,15 @@
       <c r="X312" t="inlineStr"/>
       <c r="Y312" t="inlineStr"/>
       <c r="Z312" t="inlineStr"/>
+      <c r="AA312" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB312" t="inlineStr"/>
+      <c r="AC312" t="inlineStr"/>
+      <c r="AD312" t="inlineStr"/>
+      <c r="AE312" t="inlineStr"/>
+      <c r="AF312" t="inlineStr"/>
+      <c r="AG312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -21487,6 +25263,13 @@
       <c r="X313" t="inlineStr"/>
       <c r="Y313" t="inlineStr"/>
       <c r="Z313" t="inlineStr"/>
+      <c r="AA313" t="inlineStr"/>
+      <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="inlineStr"/>
+      <c r="AD313" t="inlineStr"/>
+      <c r="AE313" t="inlineStr"/>
+      <c r="AF313" t="inlineStr"/>
+      <c r="AG313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -21551,6 +25334,17 @@
       <c r="X314" t="inlineStr"/>
       <c r="Y314" t="inlineStr"/>
       <c r="Z314" t="inlineStr"/>
+      <c r="AA314" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC314" t="inlineStr"/>
+      <c r="AD314" t="inlineStr"/>
+      <c r="AE314" t="inlineStr"/>
+      <c r="AF314" t="inlineStr"/>
+      <c r="AG314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -21639,6 +25433,25 @@
       <c r="Z315" t="n">
         <v>6</v>
       </c>
+      <c r="AA315" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -21703,6 +25516,17 @@
       <c r="X316" t="inlineStr"/>
       <c r="Y316" t="inlineStr"/>
       <c r="Z316" t="inlineStr"/>
+      <c r="AA316" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC316" t="inlineStr"/>
+      <c r="AD316" t="inlineStr"/>
+      <c r="AE316" t="inlineStr"/>
+      <c r="AF316" t="inlineStr"/>
+      <c r="AG316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -21761,6 +25585,15 @@
       <c r="X317" t="inlineStr"/>
       <c r="Y317" t="inlineStr"/>
       <c r="Z317" t="inlineStr"/>
+      <c r="AA317" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB317" t="inlineStr"/>
+      <c r="AC317" t="inlineStr"/>
+      <c r="AD317" t="inlineStr"/>
+      <c r="AE317" t="inlineStr"/>
+      <c r="AF317" t="inlineStr"/>
+      <c r="AG317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -21825,6 +25658,17 @@
       <c r="X318" t="inlineStr"/>
       <c r="Y318" t="inlineStr"/>
       <c r="Z318" t="inlineStr"/>
+      <c r="AA318" t="n">
+        <v>51</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC318" t="inlineStr"/>
+      <c r="AD318" t="inlineStr"/>
+      <c r="AE318" t="inlineStr"/>
+      <c r="AF318" t="inlineStr"/>
+      <c r="AG318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -21913,6 +25757,25 @@
       <c r="Z319" t="n">
         <v>6.12</v>
       </c>
+      <c r="AA319" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -21971,6 +25834,15 @@
       <c r="X320" t="inlineStr"/>
       <c r="Y320" t="inlineStr"/>
       <c r="Z320" t="inlineStr"/>
+      <c r="AA320" t="n">
+        <v>77</v>
+      </c>
+      <c r="AB320" t="inlineStr"/>
+      <c r="AC320" t="inlineStr"/>
+      <c r="AD320" t="inlineStr"/>
+      <c r="AE320" t="inlineStr"/>
+      <c r="AF320" t="inlineStr"/>
+      <c r="AG320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -22047,6 +25919,21 @@
       <c r="Z321" t="n">
         <v>6.08</v>
       </c>
+      <c r="AA321" t="inlineStr"/>
+      <c r="AB321" t="inlineStr"/>
+      <c r="AC321" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD321" t="inlineStr"/>
+      <c r="AE321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -22123,6 +26010,19 @@
       <c r="Z322" t="n">
         <v>0</v>
       </c>
+      <c r="AA322" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC322" t="inlineStr"/>
+      <c r="AD322" t="inlineStr"/>
+      <c r="AE322" t="inlineStr"/>
+      <c r="AF322" t="inlineStr"/>
+      <c r="AG322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -22210,6 +26110,27 @@
       </c>
       <c r="Z323" t="n">
         <v>6.06</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -22287,6 +26208,21 @@
       <c r="X324" t="inlineStr"/>
       <c r="Y324" t="inlineStr"/>
       <c r="Z324" t="inlineStr"/>
+      <c r="AA324" t="n">
+        <v>53</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE324" t="inlineStr"/>
+      <c r="AF324" t="inlineStr"/>
+      <c r="AG324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -22357,6 +26293,19 @@
       <c r="X325" t="inlineStr"/>
       <c r="Y325" t="inlineStr"/>
       <c r="Z325" t="inlineStr"/>
+      <c r="AA325" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD325" t="inlineStr"/>
+      <c r="AE325" t="inlineStr"/>
+      <c r="AF325" t="inlineStr"/>
+      <c r="AG325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -22415,6 +26364,13 @@
       <c r="X326" t="inlineStr"/>
       <c r="Y326" t="inlineStr"/>
       <c r="Z326" t="inlineStr"/>
+      <c r="AA326" t="inlineStr"/>
+      <c r="AB326" t="inlineStr"/>
+      <c r="AC326" t="inlineStr"/>
+      <c r="AD326" t="inlineStr"/>
+      <c r="AE326" t="inlineStr"/>
+      <c r="AF326" t="inlineStr"/>
+      <c r="AG326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -22485,6 +26441,19 @@
       <c r="X327" t="inlineStr"/>
       <c r="Y327" t="inlineStr"/>
       <c r="Z327" t="inlineStr"/>
+      <c r="AA327" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC327" t="inlineStr"/>
+      <c r="AD327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE327" t="inlineStr"/>
+      <c r="AF327" t="inlineStr"/>
+      <c r="AG327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -22555,6 +26524,19 @@
       <c r="X328" t="inlineStr"/>
       <c r="Y328" t="inlineStr"/>
       <c r="Z328" t="inlineStr"/>
+      <c r="AA328" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>64</v>
+      </c>
+      <c r="AD328" t="inlineStr"/>
+      <c r="AE328" t="inlineStr"/>
+      <c r="AF328" t="inlineStr"/>
+      <c r="AG328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -22637,6 +26619,25 @@
       <c r="X329" t="inlineStr"/>
       <c r="Y329" t="inlineStr"/>
       <c r="Z329" t="inlineStr"/>
+      <c r="AA329" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF329" t="inlineStr"/>
+      <c r="AG329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -22707,6 +26708,19 @@
       <c r="X330" t="inlineStr"/>
       <c r="Y330" t="inlineStr"/>
       <c r="Z330" t="inlineStr"/>
+      <c r="AA330" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>37</v>
+      </c>
+      <c r="AD330" t="inlineStr"/>
+      <c r="AE330" t="inlineStr"/>
+      <c r="AF330" t="inlineStr"/>
+      <c r="AG330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -22765,6 +26779,15 @@
       <c r="X331" t="inlineStr"/>
       <c r="Y331" t="inlineStr"/>
       <c r="Z331" t="inlineStr"/>
+      <c r="AA331" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB331" t="inlineStr"/>
+      <c r="AC331" t="inlineStr"/>
+      <c r="AD331" t="inlineStr"/>
+      <c r="AE331" t="inlineStr"/>
+      <c r="AF331" t="inlineStr"/>
+      <c r="AG331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -22817,6 +26840,13 @@
       <c r="X332" t="inlineStr"/>
       <c r="Y332" t="inlineStr"/>
       <c r="Z332" t="inlineStr"/>
+      <c r="AA332" t="inlineStr"/>
+      <c r="AB332" t="inlineStr"/>
+      <c r="AC332" t="inlineStr"/>
+      <c r="AD332" t="inlineStr"/>
+      <c r="AE332" t="inlineStr"/>
+      <c r="AF332" t="inlineStr"/>
+      <c r="AG332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -22869,6 +26899,13 @@
       <c r="X333" t="inlineStr"/>
       <c r="Y333" t="inlineStr"/>
       <c r="Z333" t="inlineStr"/>
+      <c r="AA333" t="inlineStr"/>
+      <c r="AB333" t="inlineStr"/>
+      <c r="AC333" t="inlineStr"/>
+      <c r="AD333" t="inlineStr"/>
+      <c r="AE333" t="inlineStr"/>
+      <c r="AF333" t="inlineStr"/>
+      <c r="AG333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -22957,6 +26994,25 @@
       <c r="Z334" t="n">
         <v>6.23</v>
       </c>
+      <c r="AA334" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC334" t="inlineStr"/>
+      <c r="AD334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -23039,6 +27095,23 @@
       <c r="X335" t="inlineStr"/>
       <c r="Y335" t="inlineStr"/>
       <c r="Z335" t="inlineStr"/>
+      <c r="AA335" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF335" t="inlineStr"/>
+      <c r="AG335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -23109,6 +27182,19 @@
       <c r="X336" t="inlineStr"/>
       <c r="Y336" t="inlineStr"/>
       <c r="Z336" t="inlineStr"/>
+      <c r="AA336" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD336" t="inlineStr"/>
+      <c r="AE336" t="inlineStr"/>
+      <c r="AF336" t="inlineStr"/>
+      <c r="AG336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -23173,6 +27259,15 @@
       <c r="X337" t="inlineStr"/>
       <c r="Y337" t="inlineStr"/>
       <c r="Z337" t="inlineStr"/>
+      <c r="AA337" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB337" t="inlineStr"/>
+      <c r="AC337" t="inlineStr"/>
+      <c r="AD337" t="inlineStr"/>
+      <c r="AE337" t="inlineStr"/>
+      <c r="AF337" t="inlineStr"/>
+      <c r="AG337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -23225,6 +27320,13 @@
       <c r="X338" t="inlineStr"/>
       <c r="Y338" t="inlineStr"/>
       <c r="Z338" t="inlineStr"/>
+      <c r="AA338" t="inlineStr"/>
+      <c r="AB338" t="inlineStr"/>
+      <c r="AC338" t="inlineStr"/>
+      <c r="AD338" t="inlineStr"/>
+      <c r="AE338" t="inlineStr"/>
+      <c r="AF338" t="inlineStr"/>
+      <c r="AG338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -23289,6 +27391,17 @@
       <c r="X339" t="inlineStr"/>
       <c r="Y339" t="inlineStr"/>
       <c r="Z339" t="inlineStr"/>
+      <c r="AA339" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC339" t="inlineStr"/>
+      <c r="AD339" t="inlineStr"/>
+      <c r="AE339" t="inlineStr"/>
+      <c r="AF339" t="inlineStr"/>
+      <c r="AG339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -23341,6 +27454,13 @@
       <c r="X340" t="inlineStr"/>
       <c r="Y340" t="inlineStr"/>
       <c r="Z340" t="inlineStr"/>
+      <c r="AA340" t="inlineStr"/>
+      <c r="AB340" t="inlineStr"/>
+      <c r="AC340" t="inlineStr"/>
+      <c r="AD340" t="inlineStr"/>
+      <c r="AE340" t="inlineStr"/>
+      <c r="AF340" t="inlineStr"/>
+      <c r="AG340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -23399,6 +27519,15 @@
       <c r="X341" t="inlineStr"/>
       <c r="Y341" t="inlineStr"/>
       <c r="Z341" t="inlineStr"/>
+      <c r="AA341" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB341" t="inlineStr"/>
+      <c r="AC341" t="inlineStr"/>
+      <c r="AD341" t="inlineStr"/>
+      <c r="AE341" t="inlineStr"/>
+      <c r="AF341" t="inlineStr"/>
+      <c r="AG341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -23487,6 +27616,25 @@
       <c r="Z342" t="n">
         <v>5.75</v>
       </c>
+      <c r="AA342" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -23539,6 +27687,13 @@
       <c r="X343" t="inlineStr"/>
       <c r="Y343" t="inlineStr"/>
       <c r="Z343" t="inlineStr"/>
+      <c r="AA343" t="inlineStr"/>
+      <c r="AB343" t="inlineStr"/>
+      <c r="AC343" t="inlineStr"/>
+      <c r="AD343" t="inlineStr"/>
+      <c r="AE343" t="inlineStr"/>
+      <c r="AF343" t="inlineStr"/>
+      <c r="AG343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -23603,6 +27758,15 @@
       <c r="X344" t="inlineStr"/>
       <c r="Y344" t="inlineStr"/>
       <c r="Z344" t="inlineStr"/>
+      <c r="AA344" t="inlineStr"/>
+      <c r="AB344" t="inlineStr"/>
+      <c r="AC344" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD344" t="inlineStr"/>
+      <c r="AE344" t="inlineStr"/>
+      <c r="AF344" t="inlineStr"/>
+      <c r="AG344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -23683,6 +27847,23 @@
         <v>0</v>
       </c>
       <c r="Z345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD345" t="inlineStr"/>
+      <c r="AE345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF345" t="inlineStr"/>
+      <c r="AG345" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23749,6 +27930,17 @@
       <c r="X346" t="inlineStr"/>
       <c r="Y346" t="inlineStr"/>
       <c r="Z346" t="inlineStr"/>
+      <c r="AA346" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC346" t="inlineStr"/>
+      <c r="AD346" t="inlineStr"/>
+      <c r="AE346" t="inlineStr"/>
+      <c r="AF346" t="inlineStr"/>
+      <c r="AG346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -23807,6 +27999,15 @@
       <c r="X347" t="inlineStr"/>
       <c r="Y347" t="inlineStr"/>
       <c r="Z347" t="inlineStr"/>
+      <c r="AA347" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB347" t="inlineStr"/>
+      <c r="AC347" t="inlineStr"/>
+      <c r="AD347" t="inlineStr"/>
+      <c r="AE347" t="inlineStr"/>
+      <c r="AF347" t="inlineStr"/>
+      <c r="AG347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -23883,6 +28084,21 @@
       <c r="X348" t="inlineStr"/>
       <c r="Y348" t="inlineStr"/>
       <c r="Z348" t="inlineStr"/>
+      <c r="AA348" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE348" t="inlineStr"/>
+      <c r="AF348" t="inlineStr"/>
+      <c r="AG348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -23941,6 +28157,13 @@
       <c r="X349" t="inlineStr"/>
       <c r="Y349" t="inlineStr"/>
       <c r="Z349" t="inlineStr"/>
+      <c r="AA349" t="inlineStr"/>
+      <c r="AB349" t="inlineStr"/>
+      <c r="AC349" t="inlineStr"/>
+      <c r="AD349" t="inlineStr"/>
+      <c r="AE349" t="inlineStr"/>
+      <c r="AF349" t="inlineStr"/>
+      <c r="AG349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -24005,6 +28228,17 @@
       <c r="X350" t="inlineStr"/>
       <c r="Y350" t="inlineStr"/>
       <c r="Z350" t="inlineStr"/>
+      <c r="AA350" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC350" t="inlineStr"/>
+      <c r="AD350" t="inlineStr"/>
+      <c r="AE350" t="inlineStr"/>
+      <c r="AF350" t="inlineStr"/>
+      <c r="AG350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -24063,6 +28297,15 @@
       <c r="X351" t="inlineStr"/>
       <c r="Y351" t="inlineStr"/>
       <c r="Z351" t="inlineStr"/>
+      <c r="AA351" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB351" t="inlineStr"/>
+      <c r="AC351" t="inlineStr"/>
+      <c r="AD351" t="inlineStr"/>
+      <c r="AE351" t="inlineStr"/>
+      <c r="AF351" t="inlineStr"/>
+      <c r="AG351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -24133,6 +28376,19 @@
       <c r="X352" t="inlineStr"/>
       <c r="Y352" t="inlineStr"/>
       <c r="Z352" t="inlineStr"/>
+      <c r="AA352" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD352" t="inlineStr"/>
+      <c r="AE352" t="inlineStr"/>
+      <c r="AF352" t="inlineStr"/>
+      <c r="AG352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -24191,6 +28447,13 @@
       <c r="X353" t="inlineStr"/>
       <c r="Y353" t="inlineStr"/>
       <c r="Z353" t="inlineStr"/>
+      <c r="AA353" t="inlineStr"/>
+      <c r="AB353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="inlineStr"/>
+      <c r="AE353" t="inlineStr"/>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -24243,6 +28506,13 @@
       <c r="X354" t="inlineStr"/>
       <c r="Y354" t="inlineStr"/>
       <c r="Z354" t="inlineStr"/>
+      <c r="AA354" t="inlineStr"/>
+      <c r="AB354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="inlineStr"/>
+      <c r="AE354" t="inlineStr"/>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -24295,6 +28565,13 @@
       <c r="X355" t="inlineStr"/>
       <c r="Y355" t="inlineStr"/>
       <c r="Z355" t="inlineStr"/>
+      <c r="AA355" t="inlineStr"/>
+      <c r="AB355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr"/>
+      <c r="AE355" t="inlineStr"/>
+      <c r="AF355" t="inlineStr"/>
+      <c r="AG355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -24347,6 +28624,13 @@
       <c r="X356" t="inlineStr"/>
       <c r="Y356" t="inlineStr"/>
       <c r="Z356" t="inlineStr"/>
+      <c r="AA356" t="inlineStr"/>
+      <c r="AB356" t="inlineStr"/>
+      <c r="AC356" t="inlineStr"/>
+      <c r="AD356" t="inlineStr"/>
+      <c r="AE356" t="inlineStr"/>
+      <c r="AF356" t="inlineStr"/>
+      <c r="AG356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -24411,6 +28695,15 @@
       <c r="X357" t="inlineStr"/>
       <c r="Y357" t="inlineStr"/>
       <c r="Z357" t="inlineStr"/>
+      <c r="AA357" t="inlineStr"/>
+      <c r="AB357" t="inlineStr"/>
+      <c r="AC357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD357" t="inlineStr"/>
+      <c r="AE357" t="inlineStr"/>
+      <c r="AF357" t="inlineStr"/>
+      <c r="AG357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -24463,6 +28756,13 @@
       <c r="X358" t="inlineStr"/>
       <c r="Y358" t="inlineStr"/>
       <c r="Z358" t="inlineStr"/>
+      <c r="AA358" t="inlineStr"/>
+      <c r="AB358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="inlineStr"/>
+      <c r="AE358" t="inlineStr"/>
+      <c r="AF358" t="inlineStr"/>
+      <c r="AG358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -24551,6 +28851,21 @@
       <c r="Z359" t="n">
         <v>6.03</v>
       </c>
+      <c r="AA359" t="inlineStr"/>
+      <c r="AB359" t="inlineStr"/>
+      <c r="AC359" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -24638,6 +28953,27 @@
       </c>
       <c r="Z360" t="n">
         <v>6.33</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG360" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -24709,6 +29045,19 @@
       <c r="X361" t="inlineStr"/>
       <c r="Y361" t="inlineStr"/>
       <c r="Z361" t="inlineStr"/>
+      <c r="AA361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD361" t="inlineStr"/>
+      <c r="AE361" t="inlineStr"/>
+      <c r="AF361" t="inlineStr"/>
+      <c r="AG361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -24785,6 +29134,21 @@
       <c r="X362" t="inlineStr"/>
       <c r="Y362" t="inlineStr"/>
       <c r="Z362" t="inlineStr"/>
+      <c r="AA362" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE362" t="inlineStr"/>
+      <c r="AF362" t="inlineStr"/>
+      <c r="AG362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -24849,6 +29213,17 @@
       <c r="X363" t="inlineStr"/>
       <c r="Y363" t="inlineStr"/>
       <c r="Z363" t="inlineStr"/>
+      <c r="AA363" t="n">
+        <v>43</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC363" t="inlineStr"/>
+      <c r="AD363" t="inlineStr"/>
+      <c r="AE363" t="inlineStr"/>
+      <c r="AF363" t="inlineStr"/>
+      <c r="AG363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -24930,6 +29305,25 @@
       </c>
       <c r="Z364" t="n">
         <v>6.05</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG364" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -24989,6 +29383,15 @@
       <c r="X365" t="inlineStr"/>
       <c r="Y365" t="inlineStr"/>
       <c r="Z365" t="inlineStr"/>
+      <c r="AA365" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB365" t="inlineStr"/>
+      <c r="AC365" t="inlineStr"/>
+      <c r="AD365" t="inlineStr"/>
+      <c r="AE365" t="inlineStr"/>
+      <c r="AF365" t="inlineStr"/>
+      <c r="AG365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -25059,6 +29462,19 @@
       <c r="X366" t="inlineStr"/>
       <c r="Y366" t="inlineStr"/>
       <c r="Z366" t="inlineStr"/>
+      <c r="AA366" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD366" t="inlineStr"/>
+      <c r="AE366" t="inlineStr"/>
+      <c r="AF366" t="inlineStr"/>
+      <c r="AG366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -25111,6 +29527,13 @@
       <c r="X367" t="inlineStr"/>
       <c r="Y367" t="inlineStr"/>
       <c r="Z367" t="inlineStr"/>
+      <c r="AA367" t="inlineStr"/>
+      <c r="AB367" t="inlineStr"/>
+      <c r="AC367" t="inlineStr"/>
+      <c r="AD367" t="inlineStr"/>
+      <c r="AE367" t="inlineStr"/>
+      <c r="AF367" t="inlineStr"/>
+      <c r="AG367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -25169,6 +29592,15 @@
       <c r="X368" t="inlineStr"/>
       <c r="Y368" t="inlineStr"/>
       <c r="Z368" t="inlineStr"/>
+      <c r="AA368" t="inlineStr"/>
+      <c r="AB368" t="inlineStr"/>
+      <c r="AC368" t="inlineStr"/>
+      <c r="AD368" t="inlineStr"/>
+      <c r="AE368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF368" t="inlineStr"/>
+      <c r="AG368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -25227,6 +29659,15 @@
       <c r="X369" t="inlineStr"/>
       <c r="Y369" t="inlineStr"/>
       <c r="Z369" t="inlineStr"/>
+      <c r="AA369" t="inlineStr"/>
+      <c r="AB369" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC369" t="inlineStr"/>
+      <c r="AD369" t="inlineStr"/>
+      <c r="AE369" t="inlineStr"/>
+      <c r="AF369" t="inlineStr"/>
+      <c r="AG369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -25291,6 +29732,17 @@
       <c r="X370" t="inlineStr"/>
       <c r="Y370" t="inlineStr"/>
       <c r="Z370" t="inlineStr"/>
+      <c r="AA370" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB370" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC370" t="inlineStr"/>
+      <c r="AD370" t="inlineStr"/>
+      <c r="AE370" t="inlineStr"/>
+      <c r="AF370" t="inlineStr"/>
+      <c r="AG370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -25361,6 +29813,19 @@
       <c r="X371" t="inlineStr"/>
       <c r="Y371" t="inlineStr"/>
       <c r="Z371" t="inlineStr"/>
+      <c r="AA371" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB371" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC371" t="n">
+        <v>54</v>
+      </c>
+      <c r="AD371" t="inlineStr"/>
+      <c r="AE371" t="inlineStr"/>
+      <c r="AF371" t="inlineStr"/>
+      <c r="AG371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -25448,6 +29913,27 @@
       </c>
       <c r="Z372" t="n">
         <v>6</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB372" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC372" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -25507,6 +29993,13 @@
       <c r="X373" t="inlineStr"/>
       <c r="Y373" t="inlineStr"/>
       <c r="Z373" t="inlineStr"/>
+      <c r="AA373" t="inlineStr"/>
+      <c r="AB373" t="inlineStr"/>
+      <c r="AC373" t="inlineStr"/>
+      <c r="AD373" t="inlineStr"/>
+      <c r="AE373" t="inlineStr"/>
+      <c r="AF373" t="inlineStr"/>
+      <c r="AG373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -25583,6 +30076,21 @@
       <c r="X374" t="inlineStr"/>
       <c r="Y374" t="inlineStr"/>
       <c r="Z374" t="inlineStr"/>
+      <c r="AA374" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB374" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC374" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE374" t="inlineStr"/>
+      <c r="AF374" t="inlineStr"/>
+      <c r="AG374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -25653,6 +30161,17 @@
       <c r="X375" t="inlineStr"/>
       <c r="Y375" t="inlineStr"/>
       <c r="Z375" t="inlineStr"/>
+      <c r="AA375" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC375" t="inlineStr"/>
+      <c r="AD375" t="inlineStr"/>
+      <c r="AE375" t="inlineStr"/>
+      <c r="AF375" t="inlineStr"/>
+      <c r="AG375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -25717,6 +30236,17 @@
       <c r="X376" t="inlineStr"/>
       <c r="Y376" t="inlineStr"/>
       <c r="Z376" t="inlineStr"/>
+      <c r="AA376" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB376" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC376" t="inlineStr"/>
+      <c r="AD376" t="inlineStr"/>
+      <c r="AE376" t="inlineStr"/>
+      <c r="AF376" t="inlineStr"/>
+      <c r="AG376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -25781,6 +30311,17 @@
       <c r="X377" t="inlineStr"/>
       <c r="Y377" t="inlineStr"/>
       <c r="Z377" t="inlineStr"/>
+      <c r="AA377" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB377" t="inlineStr"/>
+      <c r="AC377" t="inlineStr"/>
+      <c r="AD377" t="inlineStr"/>
+      <c r="AE377" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF377" t="inlineStr"/>
+      <c r="AG377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -25833,6 +30374,13 @@
       <c r="X378" t="inlineStr"/>
       <c r="Y378" t="inlineStr"/>
       <c r="Z378" t="inlineStr"/>
+      <c r="AA378" t="inlineStr"/>
+      <c r="AB378" t="inlineStr"/>
+      <c r="AC378" t="inlineStr"/>
+      <c r="AD378" t="inlineStr"/>
+      <c r="AE378" t="inlineStr"/>
+      <c r="AF378" t="inlineStr"/>
+      <c r="AG378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -25885,6 +30433,13 @@
       <c r="X379" t="inlineStr"/>
       <c r="Y379" t="inlineStr"/>
       <c r="Z379" t="inlineStr"/>
+      <c r="AA379" t="inlineStr"/>
+      <c r="AB379" t="inlineStr"/>
+      <c r="AC379" t="inlineStr"/>
+      <c r="AD379" t="inlineStr"/>
+      <c r="AE379" t="inlineStr"/>
+      <c r="AF379" t="inlineStr"/>
+      <c r="AG379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -25949,6 +30504,17 @@
       <c r="X380" t="inlineStr"/>
       <c r="Y380" t="inlineStr"/>
       <c r="Z380" t="inlineStr"/>
+      <c r="AA380" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB380" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC380" t="inlineStr"/>
+      <c r="AD380" t="inlineStr"/>
+      <c r="AE380" t="inlineStr"/>
+      <c r="AF380" t="inlineStr"/>
+      <c r="AG380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -26031,6 +30597,23 @@
       <c r="X381" t="inlineStr"/>
       <c r="Y381" t="inlineStr"/>
       <c r="Z381" t="inlineStr"/>
+      <c r="AA381" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB381" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC381" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF381" t="inlineStr"/>
+      <c r="AG381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -26083,6 +30666,13 @@
       <c r="X382" t="inlineStr"/>
       <c r="Y382" t="inlineStr"/>
       <c r="Z382" t="inlineStr"/>
+      <c r="AA382" t="inlineStr"/>
+      <c r="AB382" t="inlineStr"/>
+      <c r="AC382" t="inlineStr"/>
+      <c r="AD382" t="inlineStr"/>
+      <c r="AE382" t="inlineStr"/>
+      <c r="AF382" t="inlineStr"/>
+      <c r="AG382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -26135,6 +30725,13 @@
       <c r="X383" t="inlineStr"/>
       <c r="Y383" t="inlineStr"/>
       <c r="Z383" t="inlineStr"/>
+      <c r="AA383" t="inlineStr"/>
+      <c r="AB383" t="inlineStr"/>
+      <c r="AC383" t="inlineStr"/>
+      <c r="AD383" t="inlineStr"/>
+      <c r="AE383" t="inlineStr"/>
+      <c r="AF383" t="inlineStr"/>
+      <c r="AG383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -26187,6 +30784,13 @@
       <c r="X384" t="inlineStr"/>
       <c r="Y384" t="inlineStr"/>
       <c r="Z384" t="inlineStr"/>
+      <c r="AA384" t="inlineStr"/>
+      <c r="AB384" t="inlineStr"/>
+      <c r="AC384" t="inlineStr"/>
+      <c r="AD384" t="inlineStr"/>
+      <c r="AE384" t="inlineStr"/>
+      <c r="AF384" t="inlineStr"/>
+      <c r="AG384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -26269,6 +30873,21 @@
       <c r="X385" t="inlineStr"/>
       <c r="Y385" t="inlineStr"/>
       <c r="Z385" t="inlineStr"/>
+      <c r="AA385" t="n">
+        <v>62</v>
+      </c>
+      <c r="AB385" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC385" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE385" t="inlineStr"/>
+      <c r="AF385" t="inlineStr"/>
+      <c r="AG385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -26345,6 +30964,21 @@
       <c r="X386" t="inlineStr"/>
       <c r="Y386" t="inlineStr"/>
       <c r="Z386" t="inlineStr"/>
+      <c r="AA386" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB386" t="n">
+        <v>300</v>
+      </c>
+      <c r="AC386" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD386" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE386" t="inlineStr"/>
+      <c r="AF386" t="inlineStr"/>
+      <c r="AG386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -26409,6 +31043,17 @@
       <c r="X387" t="inlineStr"/>
       <c r="Y387" t="inlineStr"/>
       <c r="Z387" t="inlineStr"/>
+      <c r="AA387" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB387" t="inlineStr"/>
+      <c r="AC387" t="inlineStr"/>
+      <c r="AD387" t="inlineStr"/>
+      <c r="AE387" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF387" t="inlineStr"/>
+      <c r="AG387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -26461,6 +31106,13 @@
       <c r="X388" t="inlineStr"/>
       <c r="Y388" t="inlineStr"/>
       <c r="Z388" t="inlineStr"/>
+      <c r="AA388" t="inlineStr"/>
+      <c r="AB388" t="inlineStr"/>
+      <c r="AC388" t="inlineStr"/>
+      <c r="AD388" t="inlineStr"/>
+      <c r="AE388" t="inlineStr"/>
+      <c r="AF388" t="inlineStr"/>
+      <c r="AG388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -26537,6 +31189,21 @@
       <c r="X389" t="inlineStr"/>
       <c r="Y389" t="inlineStr"/>
       <c r="Z389" t="inlineStr"/>
+      <c r="AA389" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB389" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC389" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD389" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE389" t="inlineStr"/>
+      <c r="AF389" t="inlineStr"/>
+      <c r="AG389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -26601,6 +31268,17 @@
       <c r="X390" t="inlineStr"/>
       <c r="Y390" t="inlineStr"/>
       <c r="Z390" t="inlineStr"/>
+      <c r="AA390" t="n">
+        <v>37</v>
+      </c>
+      <c r="AB390" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC390" t="inlineStr"/>
+      <c r="AD390" t="inlineStr"/>
+      <c r="AE390" t="inlineStr"/>
+      <c r="AF390" t="inlineStr"/>
+      <c r="AG390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -26653,6 +31331,13 @@
       <c r="X391" t="inlineStr"/>
       <c r="Y391" t="inlineStr"/>
       <c r="Z391" t="inlineStr"/>
+      <c r="AA391" t="inlineStr"/>
+      <c r="AB391" t="inlineStr"/>
+      <c r="AC391" t="inlineStr"/>
+      <c r="AD391" t="inlineStr"/>
+      <c r="AE391" t="inlineStr"/>
+      <c r="AF391" t="inlineStr"/>
+      <c r="AG391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -26717,6 +31402,17 @@
       <c r="X392" t="inlineStr"/>
       <c r="Y392" t="inlineStr"/>
       <c r="Z392" t="inlineStr"/>
+      <c r="AA392" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB392" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC392" t="inlineStr"/>
+      <c r="AD392" t="inlineStr"/>
+      <c r="AE392" t="inlineStr"/>
+      <c r="AF392" t="inlineStr"/>
+      <c r="AG392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -26769,6 +31465,13 @@
       <c r="X393" t="inlineStr"/>
       <c r="Y393" t="inlineStr"/>
       <c r="Z393" t="inlineStr"/>
+      <c r="AA393" t="inlineStr"/>
+      <c r="AB393" t="inlineStr"/>
+      <c r="AC393" t="inlineStr"/>
+      <c r="AD393" t="inlineStr"/>
+      <c r="AE393" t="inlineStr"/>
+      <c r="AF393" t="inlineStr"/>
+      <c r="AG393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -26827,6 +31530,15 @@
       <c r="X394" t="inlineStr"/>
       <c r="Y394" t="inlineStr"/>
       <c r="Z394" t="inlineStr"/>
+      <c r="AA394" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB394" t="inlineStr"/>
+      <c r="AC394" t="inlineStr"/>
+      <c r="AD394" t="inlineStr"/>
+      <c r="AE394" t="inlineStr"/>
+      <c r="AF394" t="inlineStr"/>
+      <c r="AG394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -26897,6 +31609,19 @@
       <c r="X395" t="inlineStr"/>
       <c r="Y395" t="inlineStr"/>
       <c r="Z395" t="inlineStr"/>
+      <c r="AA395" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC395" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD395" t="inlineStr"/>
+      <c r="AE395" t="inlineStr"/>
+      <c r="AF395" t="inlineStr"/>
+      <c r="AG395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -26961,6 +31686,17 @@
       <c r="X396" t="inlineStr"/>
       <c r="Y396" t="inlineStr"/>
       <c r="Z396" t="inlineStr"/>
+      <c r="AA396" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC396" t="inlineStr"/>
+      <c r="AD396" t="inlineStr"/>
+      <c r="AE396" t="inlineStr"/>
+      <c r="AF396" t="inlineStr"/>
+      <c r="AG396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -27019,6 +31755,13 @@
       <c r="X397" t="inlineStr"/>
       <c r="Y397" t="inlineStr"/>
       <c r="Z397" t="inlineStr"/>
+      <c r="AA397" t="inlineStr"/>
+      <c r="AB397" t="inlineStr"/>
+      <c r="AC397" t="inlineStr"/>
+      <c r="AD397" t="inlineStr"/>
+      <c r="AE397" t="inlineStr"/>
+      <c r="AF397" t="inlineStr"/>
+      <c r="AG397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -27071,6 +31814,13 @@
       <c r="X398" t="inlineStr"/>
       <c r="Y398" t="inlineStr"/>
       <c r="Z398" t="inlineStr"/>
+      <c r="AA398" t="inlineStr"/>
+      <c r="AB398" t="inlineStr"/>
+      <c r="AC398" t="inlineStr"/>
+      <c r="AD398" t="inlineStr"/>
+      <c r="AE398" t="inlineStr"/>
+      <c r="AF398" t="inlineStr"/>
+      <c r="AG398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -27123,6 +31873,13 @@
       <c r="X399" t="inlineStr"/>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="inlineStr"/>
+      <c r="AA399" t="inlineStr"/>
+      <c r="AB399" t="inlineStr"/>
+      <c r="AC399" t="inlineStr"/>
+      <c r="AD399" t="inlineStr"/>
+      <c r="AE399" t="inlineStr"/>
+      <c r="AF399" t="inlineStr"/>
+      <c r="AG399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -27175,6 +31932,13 @@
       <c r="X400" t="inlineStr"/>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="inlineStr"/>
+      <c r="AA400" t="inlineStr"/>
+      <c r="AB400" t="inlineStr"/>
+      <c r="AC400" t="inlineStr"/>
+      <c r="AD400" t="inlineStr"/>
+      <c r="AE400" t="inlineStr"/>
+      <c r="AF400" t="inlineStr"/>
+      <c r="AG400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -27239,6 +32003,17 @@
       <c r="X401" t="inlineStr"/>
       <c r="Y401" t="inlineStr"/>
       <c r="Z401" t="inlineStr"/>
+      <c r="AA401" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB401" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC401" t="inlineStr"/>
+      <c r="AD401" t="inlineStr"/>
+      <c r="AE401" t="inlineStr"/>
+      <c r="AF401" t="inlineStr"/>
+      <c r="AG401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -27309,6 +32084,19 @@
       <c r="X402" t="inlineStr"/>
       <c r="Y402" t="inlineStr"/>
       <c r="Z402" t="inlineStr"/>
+      <c r="AA402" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB402" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC402" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD402" t="inlineStr"/>
+      <c r="AE402" t="inlineStr"/>
+      <c r="AF402" t="inlineStr"/>
+      <c r="AG402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -27361,6 +32149,13 @@
       <c r="X403" t="inlineStr"/>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="inlineStr"/>
+      <c r="AA403" t="inlineStr"/>
+      <c r="AB403" t="inlineStr"/>
+      <c r="AC403" t="inlineStr"/>
+      <c r="AD403" t="inlineStr"/>
+      <c r="AE403" t="inlineStr"/>
+      <c r="AF403" t="inlineStr"/>
+      <c r="AG403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -27431,6 +32226,19 @@
       <c r="X404" t="inlineStr"/>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="inlineStr"/>
+      <c r="AA404" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB404" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC404" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD404" t="inlineStr"/>
+      <c r="AE404" t="inlineStr"/>
+      <c r="AF404" t="inlineStr"/>
+      <c r="AG404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -27483,6 +32291,13 @@
       <c r="X405" t="inlineStr"/>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="inlineStr"/>
+      <c r="AA405" t="inlineStr"/>
+      <c r="AB405" t="inlineStr"/>
+      <c r="AC405" t="inlineStr"/>
+      <c r="AD405" t="inlineStr"/>
+      <c r="AE405" t="inlineStr"/>
+      <c r="AF405" t="inlineStr"/>
+      <c r="AG405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -27553,6 +32368,17 @@
       <c r="X406" t="inlineStr"/>
       <c r="Y406" t="inlineStr"/>
       <c r="Z406" t="inlineStr"/>
+      <c r="AA406" t="inlineStr"/>
+      <c r="AB406" t="inlineStr"/>
+      <c r="AC406" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE406" t="inlineStr"/>
+      <c r="AF406" t="inlineStr"/>
+      <c r="AG406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -27611,6 +32437,13 @@
       <c r="X407" t="inlineStr"/>
       <c r="Y407" t="inlineStr"/>
       <c r="Z407" t="inlineStr"/>
+      <c r="AA407" t="inlineStr"/>
+      <c r="AB407" t="inlineStr"/>
+      <c r="AC407" t="inlineStr"/>
+      <c r="AD407" t="inlineStr"/>
+      <c r="AE407" t="inlineStr"/>
+      <c r="AF407" t="inlineStr"/>
+      <c r="AG407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -27699,6 +32532,25 @@
       <c r="Z408" t="n">
         <v>6</v>
       </c>
+      <c r="AA408" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB408" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC408" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -27769,6 +32621,15 @@
       <c r="X409" t="inlineStr"/>
       <c r="Y409" t="inlineStr"/>
       <c r="Z409" t="inlineStr"/>
+      <c r="AA409" t="inlineStr"/>
+      <c r="AB409" t="inlineStr"/>
+      <c r="AC409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD409" t="inlineStr"/>
+      <c r="AE409" t="inlineStr"/>
+      <c r="AF409" t="inlineStr"/>
+      <c r="AG409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -27821,6 +32682,13 @@
       <c r="X410" t="inlineStr"/>
       <c r="Y410" t="inlineStr"/>
       <c r="Z410" t="inlineStr"/>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr"/>
+      <c r="AC410" t="inlineStr"/>
+      <c r="AD410" t="inlineStr"/>
+      <c r="AE410" t="inlineStr"/>
+      <c r="AF410" t="inlineStr"/>
+      <c r="AG410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -27879,6 +32747,15 @@
       <c r="X411" t="inlineStr"/>
       <c r="Y411" t="inlineStr"/>
       <c r="Z411" t="inlineStr"/>
+      <c r="AA411" t="inlineStr"/>
+      <c r="AB411" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC411" t="inlineStr"/>
+      <c r="AD411" t="inlineStr"/>
+      <c r="AE411" t="inlineStr"/>
+      <c r="AF411" t="inlineStr"/>
+      <c r="AG411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -27937,6 +32814,15 @@
       <c r="X412" t="inlineStr"/>
       <c r="Y412" t="inlineStr"/>
       <c r="Z412" t="inlineStr"/>
+      <c r="AA412" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB412" t="inlineStr"/>
+      <c r="AC412" t="inlineStr"/>
+      <c r="AD412" t="inlineStr"/>
+      <c r="AE412" t="inlineStr"/>
+      <c r="AF412" t="inlineStr"/>
+      <c r="AG412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -27995,6 +32881,13 @@
       <c r="X413" t="inlineStr"/>
       <c r="Y413" t="inlineStr"/>
       <c r="Z413" t="inlineStr"/>
+      <c r="AA413" t="inlineStr"/>
+      <c r="AB413" t="inlineStr"/>
+      <c r="AC413" t="inlineStr"/>
+      <c r="AD413" t="inlineStr"/>
+      <c r="AE413" t="inlineStr"/>
+      <c r="AF413" t="inlineStr"/>
+      <c r="AG413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -28047,6 +32940,13 @@
       <c r="X414" t="inlineStr"/>
       <c r="Y414" t="inlineStr"/>
       <c r="Z414" t="inlineStr"/>
+      <c r="AA414" t="inlineStr"/>
+      <c r="AB414" t="inlineStr"/>
+      <c r="AC414" t="inlineStr"/>
+      <c r="AD414" t="inlineStr"/>
+      <c r="AE414" t="inlineStr"/>
+      <c r="AF414" t="inlineStr"/>
+      <c r="AG414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -28099,6 +32999,13 @@
       <c r="X415" t="inlineStr"/>
       <c r="Y415" t="inlineStr"/>
       <c r="Z415" t="inlineStr"/>
+      <c r="AA415" t="inlineStr"/>
+      <c r="AB415" t="inlineStr"/>
+      <c r="AC415" t="inlineStr"/>
+      <c r="AD415" t="inlineStr"/>
+      <c r="AE415" t="inlineStr"/>
+      <c r="AF415" t="inlineStr"/>
+      <c r="AG415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -28157,6 +33064,13 @@
       <c r="X416" t="inlineStr"/>
       <c r="Y416" t="inlineStr"/>
       <c r="Z416" t="inlineStr"/>
+      <c r="AA416" t="inlineStr"/>
+      <c r="AB416" t="inlineStr"/>
+      <c r="AC416" t="inlineStr"/>
+      <c r="AD416" t="inlineStr"/>
+      <c r="AE416" t="inlineStr"/>
+      <c r="AF416" t="inlineStr"/>
+      <c r="AG416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -28209,6 +33123,13 @@
       <c r="X417" t="inlineStr"/>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="inlineStr"/>
+      <c r="AA417" t="inlineStr"/>
+      <c r="AB417" t="inlineStr"/>
+      <c r="AC417" t="inlineStr"/>
+      <c r="AD417" t="inlineStr"/>
+      <c r="AE417" t="inlineStr"/>
+      <c r="AF417" t="inlineStr"/>
+      <c r="AG417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -28261,6 +33182,13 @@
       <c r="X418" t="inlineStr"/>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="inlineStr"/>
+      <c r="AA418" t="inlineStr"/>
+      <c r="AB418" t="inlineStr"/>
+      <c r="AC418" t="inlineStr"/>
+      <c r="AD418" t="inlineStr"/>
+      <c r="AE418" t="inlineStr"/>
+      <c r="AF418" t="inlineStr"/>
+      <c r="AG418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -28319,6 +33247,15 @@
       <c r="X419" t="inlineStr"/>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="inlineStr"/>
+      <c r="AA419" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB419" t="inlineStr"/>
+      <c r="AC419" t="inlineStr"/>
+      <c r="AD419" t="inlineStr"/>
+      <c r="AE419" t="inlineStr"/>
+      <c r="AF419" t="inlineStr"/>
+      <c r="AG419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -28407,6 +33344,25 @@
       <c r="Z420" t="n">
         <v>6.17</v>
       </c>
+      <c r="AA420" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB420" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC420" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -28489,6 +33445,23 @@
       <c r="X421" t="inlineStr"/>
       <c r="Y421" t="inlineStr"/>
       <c r="Z421" t="inlineStr"/>
+      <c r="AA421" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB421" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC421" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF421" t="inlineStr"/>
+      <c r="AG421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -28547,6 +33520,15 @@
       <c r="X422" t="inlineStr"/>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="inlineStr"/>
+      <c r="AA422" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB422" t="inlineStr"/>
+      <c r="AC422" t="inlineStr"/>
+      <c r="AD422" t="inlineStr"/>
+      <c r="AE422" t="inlineStr"/>
+      <c r="AF422" t="inlineStr"/>
+      <c r="AG422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -28605,6 +33587,15 @@
       <c r="X423" t="inlineStr"/>
       <c r="Y423" t="inlineStr"/>
       <c r="Z423" t="inlineStr"/>
+      <c r="AA423" t="inlineStr"/>
+      <c r="AB423" t="inlineStr"/>
+      <c r="AC423" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD423" t="inlineStr"/>
+      <c r="AE423" t="inlineStr"/>
+      <c r="AF423" t="inlineStr"/>
+      <c r="AG423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -28657,6 +33648,13 @@
       <c r="X424" t="inlineStr"/>
       <c r="Y424" t="inlineStr"/>
       <c r="Z424" t="inlineStr"/>
+      <c r="AA424" t="inlineStr"/>
+      <c r="AB424" t="inlineStr"/>
+      <c r="AC424" t="inlineStr"/>
+      <c r="AD424" t="inlineStr"/>
+      <c r="AE424" t="inlineStr"/>
+      <c r="AF424" t="inlineStr"/>
+      <c r="AG424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -28709,6 +33707,13 @@
       <c r="X425" t="inlineStr"/>
       <c r="Y425" t="inlineStr"/>
       <c r="Z425" t="inlineStr"/>
+      <c r="AA425" t="inlineStr"/>
+      <c r="AB425" t="inlineStr"/>
+      <c r="AC425" t="inlineStr"/>
+      <c r="AD425" t="inlineStr"/>
+      <c r="AE425" t="inlineStr"/>
+      <c r="AF425" t="inlineStr"/>
+      <c r="AG425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -28767,6 +33772,13 @@
       <c r="X426" t="inlineStr"/>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="inlineStr"/>
+      <c r="AA426" t="inlineStr"/>
+      <c r="AB426" t="inlineStr"/>
+      <c r="AC426" t="inlineStr"/>
+      <c r="AD426" t="inlineStr"/>
+      <c r="AE426" t="inlineStr"/>
+      <c r="AF426" t="inlineStr"/>
+      <c r="AG426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -28819,6 +33831,13 @@
       <c r="X427" t="inlineStr"/>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="inlineStr"/>
+      <c r="AA427" t="inlineStr"/>
+      <c r="AB427" t="inlineStr"/>
+      <c r="AC427" t="inlineStr"/>
+      <c r="AD427" t="inlineStr"/>
+      <c r="AE427" t="inlineStr"/>
+      <c r="AF427" t="inlineStr"/>
+      <c r="AG427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -28871,6 +33890,13 @@
       <c r="X428" t="inlineStr"/>
       <c r="Y428" t="inlineStr"/>
       <c r="Z428" t="inlineStr"/>
+      <c r="AA428" t="inlineStr"/>
+      <c r="AB428" t="inlineStr"/>
+      <c r="AC428" t="inlineStr"/>
+      <c r="AD428" t="inlineStr"/>
+      <c r="AE428" t="inlineStr"/>
+      <c r="AF428" t="inlineStr"/>
+      <c r="AG428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -28923,6 +33949,13 @@
       <c r="X429" t="inlineStr"/>
       <c r="Y429" t="inlineStr"/>
       <c r="Z429" t="inlineStr"/>
+      <c r="AA429" t="inlineStr"/>
+      <c r="AB429" t="inlineStr"/>
+      <c r="AC429" t="inlineStr"/>
+      <c r="AD429" t="inlineStr"/>
+      <c r="AE429" t="inlineStr"/>
+      <c r="AF429" t="inlineStr"/>
+      <c r="AG429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -28975,6 +34008,13 @@
       <c r="X430" t="inlineStr"/>
       <c r="Y430" t="inlineStr"/>
       <c r="Z430" t="inlineStr"/>
+      <c r="AA430" t="inlineStr"/>
+      <c r="AB430" t="inlineStr"/>
+      <c r="AC430" t="inlineStr"/>
+      <c r="AD430" t="inlineStr"/>
+      <c r="AE430" t="inlineStr"/>
+      <c r="AF430" t="inlineStr"/>
+      <c r="AG430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -29062,6 +34102,27 @@
       </c>
       <c r="Z431" t="n">
         <v>7.29</v>
+      </c>
+      <c r="AA431" t="n">
+        <v>406</v>
+      </c>
+      <c r="AB431" t="n">
+        <v>450</v>
+      </c>
+      <c r="AC431" t="n">
+        <v>412</v>
+      </c>
+      <c r="AD431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG431" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -29127,6 +34188,17 @@
       <c r="X432" t="inlineStr"/>
       <c r="Y432" t="inlineStr"/>
       <c r="Z432" t="inlineStr"/>
+      <c r="AA432" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB432" t="n">
+        <v>320</v>
+      </c>
+      <c r="AC432" t="inlineStr"/>
+      <c r="AD432" t="inlineStr"/>
+      <c r="AE432" t="inlineStr"/>
+      <c r="AF432" t="inlineStr"/>
+      <c r="AG432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -29185,6 +34257,15 @@
       <c r="X433" t="inlineStr"/>
       <c r="Y433" t="inlineStr"/>
       <c r="Z433" t="inlineStr"/>
+      <c r="AA433" t="inlineStr"/>
+      <c r="AB433" t="inlineStr"/>
+      <c r="AC433" t="n">
+        <v>126</v>
+      </c>
+      <c r="AD433" t="inlineStr"/>
+      <c r="AE433" t="inlineStr"/>
+      <c r="AF433" t="inlineStr"/>
+      <c r="AG433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -29243,6 +34324,13 @@
       <c r="X434" t="inlineStr"/>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="inlineStr"/>
+      <c r="AA434" t="inlineStr"/>
+      <c r="AB434" t="inlineStr"/>
+      <c r="AC434" t="inlineStr"/>
+      <c r="AD434" t="inlineStr"/>
+      <c r="AE434" t="inlineStr"/>
+      <c r="AF434" t="inlineStr"/>
+      <c r="AG434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -29307,6 +34395,17 @@
       <c r="X435" t="inlineStr"/>
       <c r="Y435" t="inlineStr"/>
       <c r="Z435" t="inlineStr"/>
+      <c r="AA435" t="n">
+        <v>84</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC435" t="inlineStr"/>
+      <c r="AD435" t="inlineStr"/>
+      <c r="AE435" t="inlineStr"/>
+      <c r="AF435" t="inlineStr"/>
+      <c r="AG435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -29388,6 +34487,25 @@
       </c>
       <c r="Z436" t="n">
         <v>7.85</v>
+      </c>
+      <c r="AA436" t="inlineStr"/>
+      <c r="AB436" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>249</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG436" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -29441,6 +34559,13 @@
       <c r="X437" t="inlineStr"/>
       <c r="Y437" t="inlineStr"/>
       <c r="Z437" t="inlineStr"/>
+      <c r="AA437" t="inlineStr"/>
+      <c r="AB437" t="inlineStr"/>
+      <c r="AC437" t="inlineStr"/>
+      <c r="AD437" t="inlineStr"/>
+      <c r="AE437" t="inlineStr"/>
+      <c r="AF437" t="inlineStr"/>
+      <c r="AG437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -29505,6 +34630,17 @@
       <c r="X438" t="inlineStr"/>
       <c r="Y438" t="inlineStr"/>
       <c r="Z438" t="inlineStr"/>
+      <c r="AA438" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC438" t="inlineStr"/>
+      <c r="AD438" t="inlineStr"/>
+      <c r="AE438" t="inlineStr"/>
+      <c r="AF438" t="inlineStr"/>
+      <c r="AG438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -29569,6 +34705,17 @@
       <c r="X439" t="inlineStr"/>
       <c r="Y439" t="inlineStr"/>
       <c r="Z439" t="inlineStr"/>
+      <c r="AA439" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC439" t="inlineStr"/>
+      <c r="AD439" t="inlineStr"/>
+      <c r="AE439" t="inlineStr"/>
+      <c r="AF439" t="inlineStr"/>
+      <c r="AG439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -29651,6 +34798,23 @@
       <c r="X440" t="inlineStr"/>
       <c r="Y440" t="inlineStr"/>
       <c r="Z440" t="inlineStr"/>
+      <c r="AA440" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>330</v>
+      </c>
+      <c r="AC440" t="inlineStr"/>
+      <c r="AD440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF440" t="inlineStr"/>
+      <c r="AG440" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -29733,6 +34897,23 @@
       <c r="Z441" t="n">
         <v>7.19</v>
       </c>
+      <c r="AA441" t="inlineStr"/>
+      <c r="AB441" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -29785,6 +34966,13 @@
       <c r="X442" t="inlineStr"/>
       <c r="Y442" t="inlineStr"/>
       <c r="Z442" t="inlineStr"/>
+      <c r="AA442" t="inlineStr"/>
+      <c r="AB442" t="inlineStr"/>
+      <c r="AC442" t="inlineStr"/>
+      <c r="AD442" t="inlineStr"/>
+      <c r="AE442" t="inlineStr"/>
+      <c r="AF442" t="inlineStr"/>
+      <c r="AG442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -29872,6 +35060,27 @@
       </c>
       <c r="Z443" t="n">
         <v>7.01</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -29949,6 +35158,17 @@
       <c r="Z444" t="n">
         <v>6.67</v>
       </c>
+      <c r="AA444" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB444" t="inlineStr"/>
+      <c r="AC444" t="inlineStr"/>
+      <c r="AD444" t="inlineStr"/>
+      <c r="AE444" t="inlineStr"/>
+      <c r="AF444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -30013,6 +35233,17 @@
       <c r="X445" t="inlineStr"/>
       <c r="Y445" t="inlineStr"/>
       <c r="Z445" t="inlineStr"/>
+      <c r="AA445" t="inlineStr"/>
+      <c r="AB445" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD445" t="inlineStr"/>
+      <c r="AE445" t="inlineStr"/>
+      <c r="AF445" t="inlineStr"/>
+      <c r="AG445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -30071,6 +35302,15 @@
       <c r="X446" t="inlineStr"/>
       <c r="Y446" t="inlineStr"/>
       <c r="Z446" t="inlineStr"/>
+      <c r="AA446" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB446" t="inlineStr"/>
+      <c r="AC446" t="inlineStr"/>
+      <c r="AD446" t="inlineStr"/>
+      <c r="AE446" t="inlineStr"/>
+      <c r="AF446" t="inlineStr"/>
+      <c r="AG446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -30159,6 +35399,25 @@
       <c r="Z447" t="n">
         <v>6.78</v>
       </c>
+      <c r="AA447" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>200</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>268</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -30229,6 +35488,19 @@
       <c r="X448" t="inlineStr"/>
       <c r="Y448" t="inlineStr"/>
       <c r="Z448" t="inlineStr"/>
+      <c r="AA448" t="n">
+        <v>93</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD448" t="inlineStr"/>
+      <c r="AE448" t="inlineStr"/>
+      <c r="AF448" t="inlineStr"/>
+      <c r="AG448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -30287,6 +35559,13 @@
       <c r="X449" t="inlineStr"/>
       <c r="Y449" t="inlineStr"/>
       <c r="Z449" t="inlineStr"/>
+      <c r="AA449" t="inlineStr"/>
+      <c r="AB449" t="inlineStr"/>
+      <c r="AC449" t="inlineStr"/>
+      <c r="AD449" t="inlineStr"/>
+      <c r="AE449" t="inlineStr"/>
+      <c r="AF449" t="inlineStr"/>
+      <c r="AG449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -30339,6 +35618,13 @@
       <c r="X450" t="inlineStr"/>
       <c r="Y450" t="inlineStr"/>
       <c r="Z450" t="inlineStr"/>
+      <c r="AA450" t="inlineStr"/>
+      <c r="AB450" t="inlineStr"/>
+      <c r="AC450" t="inlineStr"/>
+      <c r="AD450" t="inlineStr"/>
+      <c r="AE450" t="inlineStr"/>
+      <c r="AF450" t="inlineStr"/>
+      <c r="AG450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -30403,6 +35689,17 @@
       <c r="X451" t="inlineStr"/>
       <c r="Y451" t="inlineStr"/>
       <c r="Z451" t="inlineStr"/>
+      <c r="AA451" t="n">
+        <v>47</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC451" t="inlineStr"/>
+      <c r="AD451" t="inlineStr"/>
+      <c r="AE451" t="inlineStr"/>
+      <c r="AF451" t="inlineStr"/>
+      <c r="AG451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -30473,6 +35770,19 @@
       <c r="X452" t="inlineStr"/>
       <c r="Y452" t="inlineStr"/>
       <c r="Z452" t="inlineStr"/>
+      <c r="AA452" t="n">
+        <v>147</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>270</v>
+      </c>
+      <c r="AC452" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD452" t="inlineStr"/>
+      <c r="AE452" t="inlineStr"/>
+      <c r="AF452" t="inlineStr"/>
+      <c r="AG452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -30555,6 +35865,23 @@
       <c r="Z453" t="n">
         <v>0</v>
       </c>
+      <c r="AA453" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC453" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE453" t="inlineStr"/>
+      <c r="AF453" t="inlineStr"/>
+      <c r="AG453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -30643,6 +35970,27 @@
       <c r="Z454" t="n">
         <v>6.46</v>
       </c>
+      <c r="AA454" t="n">
+        <v>383</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>350</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>132</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -30725,6 +36073,23 @@
       <c r="X455" t="inlineStr"/>
       <c r="Y455" t="inlineStr"/>
       <c r="Z455" t="inlineStr"/>
+      <c r="AA455" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF455" t="inlineStr"/>
+      <c r="AG455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -30783,6 +36148,13 @@
       <c r="X456" t="inlineStr"/>
       <c r="Y456" t="inlineStr"/>
       <c r="Z456" t="inlineStr"/>
+      <c r="AA456" t="inlineStr"/>
+      <c r="AB456" t="inlineStr"/>
+      <c r="AC456" t="inlineStr"/>
+      <c r="AD456" t="inlineStr"/>
+      <c r="AE456" t="inlineStr"/>
+      <c r="AF456" t="inlineStr"/>
+      <c r="AG456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -30870,6 +36242,27 @@
       </c>
       <c r="Z457" t="n">
         <v>6.12</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>97</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>110</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG457" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -30929,6 +36322,15 @@
       <c r="X458" t="inlineStr"/>
       <c r="Y458" t="inlineStr"/>
       <c r="Z458" t="inlineStr"/>
+      <c r="AA458" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB458" t="inlineStr"/>
+      <c r="AC458" t="inlineStr"/>
+      <c r="AD458" t="inlineStr"/>
+      <c r="AE458" t="inlineStr"/>
+      <c r="AF458" t="inlineStr"/>
+      <c r="AG458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -30981,6 +36383,13 @@
       <c r="X459" t="inlineStr"/>
       <c r="Y459" t="inlineStr"/>
       <c r="Z459" t="inlineStr"/>
+      <c r="AA459" t="inlineStr"/>
+      <c r="AB459" t="inlineStr"/>
+      <c r="AC459" t="inlineStr"/>
+      <c r="AD459" t="inlineStr"/>
+      <c r="AE459" t="inlineStr"/>
+      <c r="AF459" t="inlineStr"/>
+      <c r="AG459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -31033,6 +36442,13 @@
       <c r="X460" t="inlineStr"/>
       <c r="Y460" t="inlineStr"/>
       <c r="Z460" t="inlineStr"/>
+      <c r="AA460" t="inlineStr"/>
+      <c r="AB460" t="inlineStr"/>
+      <c r="AC460" t="inlineStr"/>
+      <c r="AD460" t="inlineStr"/>
+      <c r="AE460" t="inlineStr"/>
+      <c r="AF460" t="inlineStr"/>
+      <c r="AG460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -31103,6 +36519,19 @@
       <c r="X461" t="inlineStr"/>
       <c r="Y461" t="inlineStr"/>
       <c r="Z461" t="inlineStr"/>
+      <c r="AA461" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC461" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD461" t="inlineStr"/>
+      <c r="AE461" t="inlineStr"/>
+      <c r="AF461" t="inlineStr"/>
+      <c r="AG461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -31191,6 +36620,25 @@
       <c r="Z462" t="n">
         <v>7.07</v>
       </c>
+      <c r="AA462" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC462" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -31279,6 +36727,23 @@
       <c r="Z463" t="n">
         <v>8.33</v>
       </c>
+      <c r="AA463" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>260</v>
+      </c>
+      <c r="AC463" t="n">
+        <v>252</v>
+      </c>
+      <c r="AD463" t="inlineStr"/>
+      <c r="AE463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -31361,6 +36826,21 @@
       <c r="Z464" t="n">
         <v>0</v>
       </c>
+      <c r="AA464" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC464" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD464" t="inlineStr"/>
+      <c r="AE464" t="inlineStr"/>
+      <c r="AF464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -31425,6 +36905,17 @@
       <c r="X465" t="inlineStr"/>
       <c r="Y465" t="inlineStr"/>
       <c r="Z465" t="inlineStr"/>
+      <c r="AA465" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC465" t="inlineStr"/>
+      <c r="AD465" t="inlineStr"/>
+      <c r="AE465" t="inlineStr"/>
+      <c r="AF465" t="inlineStr"/>
+      <c r="AG465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -31477,6 +36968,13 @@
       <c r="X466" t="inlineStr"/>
       <c r="Y466" t="inlineStr"/>
       <c r="Z466" t="inlineStr"/>
+      <c r="AA466" t="inlineStr"/>
+      <c r="AB466" t="inlineStr"/>
+      <c r="AC466" t="inlineStr"/>
+      <c r="AD466" t="inlineStr"/>
+      <c r="AE466" t="inlineStr"/>
+      <c r="AF466" t="inlineStr"/>
+      <c r="AG466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -31541,6 +37039,17 @@
       <c r="X467" t="inlineStr"/>
       <c r="Y467" t="inlineStr"/>
       <c r="Z467" t="inlineStr"/>
+      <c r="AA467" t="n">
+        <v>79</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC467" t="inlineStr"/>
+      <c r="AD467" t="inlineStr"/>
+      <c r="AE467" t="inlineStr"/>
+      <c r="AF467" t="inlineStr"/>
+      <c r="AG467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -31593,6 +37102,13 @@
       <c r="X468" t="inlineStr"/>
       <c r="Y468" t="inlineStr"/>
       <c r="Z468" t="inlineStr"/>
+      <c r="AA468" t="inlineStr"/>
+      <c r="AB468" t="inlineStr"/>
+      <c r="AC468" t="inlineStr"/>
+      <c r="AD468" t="inlineStr"/>
+      <c r="AE468" t="inlineStr"/>
+      <c r="AF468" t="inlineStr"/>
+      <c r="AG468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -31680,6 +37196,27 @@
       </c>
       <c r="Z469" t="n">
         <v>7.84</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>279</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>330</v>
+      </c>
+      <c r="AC469" t="n">
+        <v>259</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG469" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -31733,6 +37270,13 @@
       <c r="X470" t="inlineStr"/>
       <c r="Y470" t="inlineStr"/>
       <c r="Z470" t="inlineStr"/>
+      <c r="AA470" t="inlineStr"/>
+      <c r="AB470" t="inlineStr"/>
+      <c r="AC470" t="inlineStr"/>
+      <c r="AD470" t="inlineStr"/>
+      <c r="AE470" t="inlineStr"/>
+      <c r="AF470" t="inlineStr"/>
+      <c r="AG470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -31785,6 +37329,13 @@
       <c r="X471" t="inlineStr"/>
       <c r="Y471" t="inlineStr"/>
       <c r="Z471" t="inlineStr"/>
+      <c r="AA471" t="inlineStr"/>
+      <c r="AB471" t="inlineStr"/>
+      <c r="AC471" t="inlineStr"/>
+      <c r="AD471" t="inlineStr"/>
+      <c r="AE471" t="inlineStr"/>
+      <c r="AF471" t="inlineStr"/>
+      <c r="AG471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -31861,6 +37412,21 @@
       <c r="Z472" t="n">
         <v>0</v>
       </c>
+      <c r="AA472" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC472" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD472" t="inlineStr"/>
+      <c r="AE472" t="inlineStr"/>
+      <c r="AF472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -31919,6 +37485,13 @@
       <c r="X473" t="inlineStr"/>
       <c r="Y473" t="inlineStr"/>
       <c r="Z473" t="inlineStr"/>
+      <c r="AA473" t="inlineStr"/>
+      <c r="AB473" t="inlineStr"/>
+      <c r="AC473" t="inlineStr"/>
+      <c r="AD473" t="inlineStr"/>
+      <c r="AE473" t="inlineStr"/>
+      <c r="AF473" t="inlineStr"/>
+      <c r="AG473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -31989,6 +37562,19 @@
       <c r="X474" t="inlineStr"/>
       <c r="Y474" t="inlineStr"/>
       <c r="Z474" t="inlineStr"/>
+      <c r="AA474" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC474" t="inlineStr"/>
+      <c r="AD474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE474" t="inlineStr"/>
+      <c r="AF474" t="inlineStr"/>
+      <c r="AG474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -32047,6 +37633,13 @@
       <c r="X475" t="inlineStr"/>
       <c r="Y475" t="inlineStr"/>
       <c r="Z475" t="inlineStr"/>
+      <c r="AA475" t="inlineStr"/>
+      <c r="AB475" t="inlineStr"/>
+      <c r="AC475" t="inlineStr"/>
+      <c r="AD475" t="inlineStr"/>
+      <c r="AE475" t="inlineStr"/>
+      <c r="AF475" t="inlineStr"/>
+      <c r="AG475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -32105,6 +37698,13 @@
       <c r="X476" t="inlineStr"/>
       <c r="Y476" t="inlineStr"/>
       <c r="Z476" t="inlineStr"/>
+      <c r="AA476" t="inlineStr"/>
+      <c r="AB476" t="inlineStr"/>
+      <c r="AC476" t="inlineStr"/>
+      <c r="AD476" t="inlineStr"/>
+      <c r="AE476" t="inlineStr"/>
+      <c r="AF476" t="inlineStr"/>
+      <c r="AG476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -32181,6 +37781,21 @@
       <c r="X477" t="inlineStr"/>
       <c r="Y477" t="inlineStr"/>
       <c r="Z477" t="inlineStr"/>
+      <c r="AA477" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB477" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC477" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE477" t="inlineStr"/>
+      <c r="AF477" t="inlineStr"/>
+      <c r="AG477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -32245,6 +37860,15 @@
       <c r="X478" t="inlineStr"/>
       <c r="Y478" t="inlineStr"/>
       <c r="Z478" t="inlineStr"/>
+      <c r="AA478" t="inlineStr"/>
+      <c r="AB478" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC478" t="inlineStr"/>
+      <c r="AD478" t="inlineStr"/>
+      <c r="AE478" t="inlineStr"/>
+      <c r="AF478" t="inlineStr"/>
+      <c r="AG478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -32321,6 +37945,23 @@
       <c r="Z479" t="n">
         <v>7.21</v>
       </c>
+      <c r="AA479" t="inlineStr"/>
+      <c r="AB479" t="inlineStr"/>
+      <c r="AC479" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG479" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -32391,6 +38032,19 @@
       <c r="X480" t="inlineStr"/>
       <c r="Y480" t="inlineStr"/>
       <c r="Z480" t="inlineStr"/>
+      <c r="AA480" t="inlineStr"/>
+      <c r="AB480" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC480" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD480" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE480" t="inlineStr"/>
+      <c r="AF480" t="inlineStr"/>
+      <c r="AG480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -32449,6 +38103,15 @@
       <c r="X481" t="inlineStr"/>
       <c r="Y481" t="inlineStr"/>
       <c r="Z481" t="inlineStr"/>
+      <c r="AA481" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB481" t="inlineStr"/>
+      <c r="AC481" t="inlineStr"/>
+      <c r="AD481" t="inlineStr"/>
+      <c r="AE481" t="inlineStr"/>
+      <c r="AF481" t="inlineStr"/>
+      <c r="AG481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -32507,6 +38170,15 @@
       <c r="X482" t="inlineStr"/>
       <c r="Y482" t="inlineStr"/>
       <c r="Z482" t="inlineStr"/>
+      <c r="AA482" t="n">
+        <v>238</v>
+      </c>
+      <c r="AB482" t="inlineStr"/>
+      <c r="AC482" t="inlineStr"/>
+      <c r="AD482" t="inlineStr"/>
+      <c r="AE482" t="inlineStr"/>
+      <c r="AF482" t="inlineStr"/>
+      <c r="AG482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -32559,6 +38231,13 @@
       <c r="X483" t="inlineStr"/>
       <c r="Y483" t="inlineStr"/>
       <c r="Z483" t="inlineStr"/>
+      <c r="AA483" t="inlineStr"/>
+      <c r="AB483" t="inlineStr"/>
+      <c r="AC483" t="inlineStr"/>
+      <c r="AD483" t="inlineStr"/>
+      <c r="AE483" t="inlineStr"/>
+      <c r="AF483" t="inlineStr"/>
+      <c r="AG483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -32641,6 +38320,21 @@
       <c r="X484" t="inlineStr"/>
       <c r="Y484" t="inlineStr"/>
       <c r="Z484" t="inlineStr"/>
+      <c r="AA484" t="inlineStr"/>
+      <c r="AB484" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC484" t="n">
+        <v>146</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF484" t="inlineStr"/>
+      <c r="AG484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -32693,6 +38387,13 @@
       <c r="X485" t="inlineStr"/>
       <c r="Y485" t="inlineStr"/>
       <c r="Z485" t="inlineStr"/>
+      <c r="AA485" t="inlineStr"/>
+      <c r="AB485" t="inlineStr"/>
+      <c r="AC485" t="inlineStr"/>
+      <c r="AD485" t="inlineStr"/>
+      <c r="AE485" t="inlineStr"/>
+      <c r="AF485" t="inlineStr"/>
+      <c r="AG485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -32745,6 +38446,13 @@
       <c r="X486" t="inlineStr"/>
       <c r="Y486" t="inlineStr"/>
       <c r="Z486" t="inlineStr"/>
+      <c r="AA486" t="inlineStr"/>
+      <c r="AB486" t="inlineStr"/>
+      <c r="AC486" t="inlineStr"/>
+      <c r="AD486" t="inlineStr"/>
+      <c r="AE486" t="inlineStr"/>
+      <c r="AF486" t="inlineStr"/>
+      <c r="AG486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -32797,6 +38505,13 @@
       <c r="X487" t="inlineStr"/>
       <c r="Y487" t="inlineStr"/>
       <c r="Z487" t="inlineStr"/>
+      <c r="AA487" t="inlineStr"/>
+      <c r="AB487" t="inlineStr"/>
+      <c r="AC487" t="inlineStr"/>
+      <c r="AD487" t="inlineStr"/>
+      <c r="AE487" t="inlineStr"/>
+      <c r="AF487" t="inlineStr"/>
+      <c r="AG487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -32849,6 +38564,13 @@
       <c r="X488" t="inlineStr"/>
       <c r="Y488" t="inlineStr"/>
       <c r="Z488" t="inlineStr"/>
+      <c r="AA488" t="inlineStr"/>
+      <c r="AB488" t="inlineStr"/>
+      <c r="AC488" t="inlineStr"/>
+      <c r="AD488" t="inlineStr"/>
+      <c r="AE488" t="inlineStr"/>
+      <c r="AF488" t="inlineStr"/>
+      <c r="AG488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -32936,6 +38658,27 @@
       </c>
       <c r="Z489" t="n">
         <v>5.5</v>
+      </c>
+      <c r="AA489" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB489" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC489" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG489" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -32989,6 +38732,13 @@
       <c r="X490" t="inlineStr"/>
       <c r="Y490" t="inlineStr"/>
       <c r="Z490" t="inlineStr"/>
+      <c r="AA490" t="inlineStr"/>
+      <c r="AB490" t="inlineStr"/>
+      <c r="AC490" t="inlineStr"/>
+      <c r="AD490" t="inlineStr"/>
+      <c r="AE490" t="inlineStr"/>
+      <c r="AF490" t="inlineStr"/>
+      <c r="AG490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -33076,6 +38826,27 @@
       </c>
       <c r="Z491" t="n">
         <v>8.66</v>
+      </c>
+      <c r="AA491" t="n">
+        <v>172</v>
+      </c>
+      <c r="AB491" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC491" t="n">
+        <v>62</v>
+      </c>
+      <c r="AD491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG491" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="492">
@@ -33129,6 +38900,13 @@
       <c r="X492" t="inlineStr"/>
       <c r="Y492" t="inlineStr"/>
       <c r="Z492" t="inlineStr"/>
+      <c r="AA492" t="inlineStr"/>
+      <c r="AB492" t="inlineStr"/>
+      <c r="AC492" t="inlineStr"/>
+      <c r="AD492" t="inlineStr"/>
+      <c r="AE492" t="inlineStr"/>
+      <c r="AF492" t="inlineStr"/>
+      <c r="AG492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -33181,6 +38959,13 @@
       <c r="X493" t="inlineStr"/>
       <c r="Y493" t="inlineStr"/>
       <c r="Z493" t="inlineStr"/>
+      <c r="AA493" t="inlineStr"/>
+      <c r="AB493" t="inlineStr"/>
+      <c r="AC493" t="inlineStr"/>
+      <c r="AD493" t="inlineStr"/>
+      <c r="AE493" t="inlineStr"/>
+      <c r="AF493" t="inlineStr"/>
+      <c r="AG493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -33233,6 +39018,13 @@
       <c r="X494" t="inlineStr"/>
       <c r="Y494" t="inlineStr"/>
       <c r="Z494" t="inlineStr"/>
+      <c r="AA494" t="inlineStr"/>
+      <c r="AB494" t="inlineStr"/>
+      <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="inlineStr"/>
+      <c r="AE494" t="inlineStr"/>
+      <c r="AF494" t="inlineStr"/>
+      <c r="AG494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -33291,6 +39083,13 @@
       <c r="X495" t="inlineStr"/>
       <c r="Y495" t="inlineStr"/>
       <c r="Z495" t="inlineStr"/>
+      <c r="AA495" t="inlineStr"/>
+      <c r="AB495" t="inlineStr"/>
+      <c r="AC495" t="inlineStr"/>
+      <c r="AD495" t="inlineStr"/>
+      <c r="AE495" t="inlineStr"/>
+      <c r="AF495" t="inlineStr"/>
+      <c r="AG495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -33343,6 +39142,13 @@
       <c r="X496" t="inlineStr"/>
       <c r="Y496" t="inlineStr"/>
       <c r="Z496" t="inlineStr"/>
+      <c r="AA496" t="inlineStr"/>
+      <c r="AB496" t="inlineStr"/>
+      <c r="AC496" t="inlineStr"/>
+      <c r="AD496" t="inlineStr"/>
+      <c r="AE496" t="inlineStr"/>
+      <c r="AF496" t="inlineStr"/>
+      <c r="AG496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -33401,6 +39207,15 @@
       <c r="X497" t="inlineStr"/>
       <c r="Y497" t="inlineStr"/>
       <c r="Z497" t="inlineStr"/>
+      <c r="AA497" t="n">
+        <v>94</v>
+      </c>
+      <c r="AB497" t="inlineStr"/>
+      <c r="AC497" t="inlineStr"/>
+      <c r="AD497" t="inlineStr"/>
+      <c r="AE497" t="inlineStr"/>
+      <c r="AF497" t="inlineStr"/>
+      <c r="AG497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -33453,6 +39268,13 @@
       <c r="X498" t="inlineStr"/>
       <c r="Y498" t="inlineStr"/>
       <c r="Z498" t="inlineStr"/>
+      <c r="AA498" t="inlineStr"/>
+      <c r="AB498" t="inlineStr"/>
+      <c r="AC498" t="inlineStr"/>
+      <c r="AD498" t="inlineStr"/>
+      <c r="AE498" t="inlineStr"/>
+      <c r="AF498" t="inlineStr"/>
+      <c r="AG498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -33523,6 +39345,19 @@
       <c r="X499" t="inlineStr"/>
       <c r="Y499" t="inlineStr"/>
       <c r="Z499" t="inlineStr"/>
+      <c r="AA499" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB499" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC499" t="n">
+        <v>181</v>
+      </c>
+      <c r="AD499" t="inlineStr"/>
+      <c r="AE499" t="inlineStr"/>
+      <c r="AF499" t="inlineStr"/>
+      <c r="AG499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -33581,6 +39416,13 @@
       <c r="X500" t="inlineStr"/>
       <c r="Y500" t="inlineStr"/>
       <c r="Z500" t="inlineStr"/>
+      <c r="AA500" t="inlineStr"/>
+      <c r="AB500" t="inlineStr"/>
+      <c r="AC500" t="inlineStr"/>
+      <c r="AD500" t="inlineStr"/>
+      <c r="AE500" t="inlineStr"/>
+      <c r="AF500" t="inlineStr"/>
+      <c r="AG500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -33633,6 +39475,13 @@
       <c r="X501" t="inlineStr"/>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" t="inlineStr"/>
+      <c r="AA501" t="inlineStr"/>
+      <c r="AB501" t="inlineStr"/>
+      <c r="AC501" t="inlineStr"/>
+      <c r="AD501" t="inlineStr"/>
+      <c r="AE501" t="inlineStr"/>
+      <c r="AF501" t="inlineStr"/>
+      <c r="AG501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -33685,6 +39534,13 @@
       <c r="X502" t="inlineStr"/>
       <c r="Y502" t="inlineStr"/>
       <c r="Z502" t="inlineStr"/>
+      <c r="AA502" t="inlineStr"/>
+      <c r="AB502" t="inlineStr"/>
+      <c r="AC502" t="inlineStr"/>
+      <c r="AD502" t="inlineStr"/>
+      <c r="AE502" t="inlineStr"/>
+      <c r="AF502" t="inlineStr"/>
+      <c r="AG502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -33761,6 +39617,21 @@
       <c r="X503" t="inlineStr"/>
       <c r="Y503" t="inlineStr"/>
       <c r="Z503" t="inlineStr"/>
+      <c r="AA503" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB503" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC503" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD503" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE503" t="inlineStr"/>
+      <c r="AF503" t="inlineStr"/>
+      <c r="AG503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -33813,6 +39684,13 @@
       <c r="X504" t="inlineStr"/>
       <c r="Y504" t="inlineStr"/>
       <c r="Z504" t="inlineStr"/>
+      <c r="AA504" t="inlineStr"/>
+      <c r="AB504" t="inlineStr"/>
+      <c r="AC504" t="inlineStr"/>
+      <c r="AD504" t="inlineStr"/>
+      <c r="AE504" t="inlineStr"/>
+      <c r="AF504" t="inlineStr"/>
+      <c r="AG504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -33900,6 +39778,27 @@
       </c>
       <c r="Z505" t="n">
         <v>7.41</v>
+      </c>
+      <c r="AA505" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB505" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC505" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG505" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="506">
@@ -33953,6 +39852,13 @@
       <c r="X506" t="inlineStr"/>
       <c r="Y506" t="inlineStr"/>
       <c r="Z506" t="inlineStr"/>
+      <c r="AA506" t="inlineStr"/>
+      <c r="AB506" t="inlineStr"/>
+      <c r="AC506" t="inlineStr"/>
+      <c r="AD506" t="inlineStr"/>
+      <c r="AE506" t="inlineStr"/>
+      <c r="AF506" t="inlineStr"/>
+      <c r="AG506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -34005,6 +39911,13 @@
       <c r="X507" t="inlineStr"/>
       <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="inlineStr"/>
+      <c r="AA507" t="inlineStr"/>
+      <c r="AB507" t="inlineStr"/>
+      <c r="AC507" t="inlineStr"/>
+      <c r="AD507" t="inlineStr"/>
+      <c r="AE507" t="inlineStr"/>
+      <c r="AF507" t="inlineStr"/>
+      <c r="AG507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -34092,6 +40005,27 @@
       </c>
       <c r="Z508" t="n">
         <v>6.8</v>
+      </c>
+      <c r="AA508" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB508" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC508" t="n">
+        <v>133</v>
+      </c>
+      <c r="AD508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG508" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="509">
@@ -34151,6 +40085,15 @@
       <c r="X509" t="inlineStr"/>
       <c r="Y509" t="inlineStr"/>
       <c r="Z509" t="inlineStr"/>
+      <c r="AA509" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB509" t="inlineStr"/>
+      <c r="AC509" t="inlineStr"/>
+      <c r="AD509" t="inlineStr"/>
+      <c r="AE509" t="inlineStr"/>
+      <c r="AF509" t="inlineStr"/>
+      <c r="AG509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -34209,6 +40152,15 @@
       <c r="X510" t="inlineStr"/>
       <c r="Y510" t="inlineStr"/>
       <c r="Z510" t="inlineStr"/>
+      <c r="AA510" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB510" t="inlineStr"/>
+      <c r="AC510" t="inlineStr"/>
+      <c r="AD510" t="inlineStr"/>
+      <c r="AE510" t="inlineStr"/>
+      <c r="AF510" t="inlineStr"/>
+      <c r="AG510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -34261,6 +40213,13 @@
       <c r="X511" t="inlineStr"/>
       <c r="Y511" t="inlineStr"/>
       <c r="Z511" t="inlineStr"/>
+      <c r="AA511" t="inlineStr"/>
+      <c r="AB511" t="inlineStr"/>
+      <c r="AC511" t="inlineStr"/>
+      <c r="AD511" t="inlineStr"/>
+      <c r="AE511" t="inlineStr"/>
+      <c r="AF511" t="inlineStr"/>
+      <c r="AG511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -34313,6 +40272,13 @@
       <c r="X512" t="inlineStr"/>
       <c r="Y512" t="inlineStr"/>
       <c r="Z512" t="inlineStr"/>
+      <c r="AA512" t="inlineStr"/>
+      <c r="AB512" t="inlineStr"/>
+      <c r="AC512" t="inlineStr"/>
+      <c r="AD512" t="inlineStr"/>
+      <c r="AE512" t="inlineStr"/>
+      <c r="AF512" t="inlineStr"/>
+      <c r="AG512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -34365,6 +40331,13 @@
       <c r="X513" t="inlineStr"/>
       <c r="Y513" t="inlineStr"/>
       <c r="Z513" t="inlineStr"/>
+      <c r="AA513" t="inlineStr"/>
+      <c r="AB513" t="inlineStr"/>
+      <c r="AC513" t="inlineStr"/>
+      <c r="AD513" t="inlineStr"/>
+      <c r="AE513" t="inlineStr"/>
+      <c r="AF513" t="inlineStr"/>
+      <c r="AG513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -34423,6 +40396,15 @@
       <c r="X514" t="inlineStr"/>
       <c r="Y514" t="inlineStr"/>
       <c r="Z514" t="inlineStr"/>
+      <c r="AA514" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB514" t="inlineStr"/>
+      <c r="AC514" t="inlineStr"/>
+      <c r="AD514" t="inlineStr"/>
+      <c r="AE514" t="inlineStr"/>
+      <c r="AF514" t="inlineStr"/>
+      <c r="AG514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -34504,6 +40486,25 @@
       </c>
       <c r="Z515" t="n">
         <v>5.5</v>
+      </c>
+      <c r="AA515" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB515" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC515" t="inlineStr"/>
+      <c r="AD515" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE515" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF515" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG515" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -34569,6 +40570,17 @@
       <c r="X516" t="inlineStr"/>
       <c r="Y516" t="inlineStr"/>
       <c r="Z516" t="inlineStr"/>
+      <c r="AA516" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB516" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC516" t="inlineStr"/>
+      <c r="AD516" t="inlineStr"/>
+      <c r="AE516" t="inlineStr"/>
+      <c r="AF516" t="inlineStr"/>
+      <c r="AG516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -34633,6 +40645,17 @@
       <c r="X517" t="inlineStr"/>
       <c r="Y517" t="inlineStr"/>
       <c r="Z517" t="inlineStr"/>
+      <c r="AA517" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB517" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC517" t="inlineStr"/>
+      <c r="AD517" t="inlineStr"/>
+      <c r="AE517" t="inlineStr"/>
+      <c r="AF517" t="inlineStr"/>
+      <c r="AG517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -34685,6 +40708,13 @@
       <c r="X518" t="inlineStr"/>
       <c r="Y518" t="inlineStr"/>
       <c r="Z518" t="inlineStr"/>
+      <c r="AA518" t="inlineStr"/>
+      <c r="AB518" t="inlineStr"/>
+      <c r="AC518" t="inlineStr"/>
+      <c r="AD518" t="inlineStr"/>
+      <c r="AE518" t="inlineStr"/>
+      <c r="AF518" t="inlineStr"/>
+      <c r="AG518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -34755,6 +40785,19 @@
       <c r="X519" t="inlineStr"/>
       <c r="Y519" t="inlineStr"/>
       <c r="Z519" t="inlineStr"/>
+      <c r="AA519" t="n">
+        <v>181</v>
+      </c>
+      <c r="AB519" t="inlineStr"/>
+      <c r="AC519" t="inlineStr"/>
+      <c r="AD519" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE519" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF519" t="inlineStr"/>
+      <c r="AG519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -34807,6 +40850,13 @@
       <c r="X520" t="inlineStr"/>
       <c r="Y520" t="inlineStr"/>
       <c r="Z520" t="inlineStr"/>
+      <c r="AA520" t="inlineStr"/>
+      <c r="AB520" t="inlineStr"/>
+      <c r="AC520" t="inlineStr"/>
+      <c r="AD520" t="inlineStr"/>
+      <c r="AE520" t="inlineStr"/>
+      <c r="AF520" t="inlineStr"/>
+      <c r="AG520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -34859,6 +40909,13 @@
       <c r="X521" t="inlineStr"/>
       <c r="Y521" t="inlineStr"/>
       <c r="Z521" t="inlineStr"/>
+      <c r="AA521" t="inlineStr"/>
+      <c r="AB521" t="inlineStr"/>
+      <c r="AC521" t="inlineStr"/>
+      <c r="AD521" t="inlineStr"/>
+      <c r="AE521" t="inlineStr"/>
+      <c r="AF521" t="inlineStr"/>
+      <c r="AG521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -34911,6 +40968,13 @@
       <c r="X522" t="inlineStr"/>
       <c r="Y522" t="inlineStr"/>
       <c r="Z522" t="inlineStr"/>
+      <c r="AA522" t="inlineStr"/>
+      <c r="AB522" t="inlineStr"/>
+      <c r="AC522" t="inlineStr"/>
+      <c r="AD522" t="inlineStr"/>
+      <c r="AE522" t="inlineStr"/>
+      <c r="AF522" t="inlineStr"/>
+      <c r="AG522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -34963,6 +41027,13 @@
       <c r="X523" t="inlineStr"/>
       <c r="Y523" t="inlineStr"/>
       <c r="Z523" t="inlineStr"/>
+      <c r="AA523" t="inlineStr"/>
+      <c r="AB523" t="inlineStr"/>
+      <c r="AC523" t="inlineStr"/>
+      <c r="AD523" t="inlineStr"/>
+      <c r="AE523" t="inlineStr"/>
+      <c r="AF523" t="inlineStr"/>
+      <c r="AG523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -35044,6 +41115,23 @@
       </c>
       <c r="Z524" t="n">
         <v>7.27</v>
+      </c>
+      <c r="AA524" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB524" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC524" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD524" t="inlineStr"/>
+      <c r="AE524" t="inlineStr"/>
+      <c r="AF524" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG524" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -35097,6 +41185,13 @@
       <c r="X525" t="inlineStr"/>
       <c r="Y525" t="inlineStr"/>
       <c r="Z525" t="inlineStr"/>
+      <c r="AA525" t="inlineStr"/>
+      <c r="AB525" t="inlineStr"/>
+      <c r="AC525" t="inlineStr"/>
+      <c r="AD525" t="inlineStr"/>
+      <c r="AE525" t="inlineStr"/>
+      <c r="AF525" t="inlineStr"/>
+      <c r="AG525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -35149,6 +41244,13 @@
       <c r="X526" t="inlineStr"/>
       <c r="Y526" t="inlineStr"/>
       <c r="Z526" t="inlineStr"/>
+      <c r="AA526" t="inlineStr"/>
+      <c r="AB526" t="inlineStr"/>
+      <c r="AC526" t="inlineStr"/>
+      <c r="AD526" t="inlineStr"/>
+      <c r="AE526" t="inlineStr"/>
+      <c r="AF526" t="inlineStr"/>
+      <c r="AG526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -35201,6 +41303,13 @@
       <c r="X527" t="inlineStr"/>
       <c r="Y527" t="inlineStr"/>
       <c r="Z527" t="inlineStr"/>
+      <c r="AA527" t="inlineStr"/>
+      <c r="AB527" t="inlineStr"/>
+      <c r="AC527" t="inlineStr"/>
+      <c r="AD527" t="inlineStr"/>
+      <c r="AE527" t="inlineStr"/>
+      <c r="AF527" t="inlineStr"/>
+      <c r="AG527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -35253,6 +41362,13 @@
       <c r="X528" t="inlineStr"/>
       <c r="Y528" t="inlineStr"/>
       <c r="Z528" t="inlineStr"/>
+      <c r="AA528" t="inlineStr"/>
+      <c r="AB528" t="inlineStr"/>
+      <c r="AC528" t="inlineStr"/>
+      <c r="AD528" t="inlineStr"/>
+      <c r="AE528" t="inlineStr"/>
+      <c r="AF528" t="inlineStr"/>
+      <c r="AG528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -35305,6 +41421,13 @@
       <c r="X529" t="inlineStr"/>
       <c r="Y529" t="inlineStr"/>
       <c r="Z529" t="inlineStr"/>
+      <c r="AA529" t="inlineStr"/>
+      <c r="AB529" t="inlineStr"/>
+      <c r="AC529" t="inlineStr"/>
+      <c r="AD529" t="inlineStr"/>
+      <c r="AE529" t="inlineStr"/>
+      <c r="AF529" t="inlineStr"/>
+      <c r="AG529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -35357,6 +41480,13 @@
       <c r="X530" t="inlineStr"/>
       <c r="Y530" t="inlineStr"/>
       <c r="Z530" t="inlineStr"/>
+      <c r="AA530" t="inlineStr"/>
+      <c r="AB530" t="inlineStr"/>
+      <c r="AC530" t="inlineStr"/>
+      <c r="AD530" t="inlineStr"/>
+      <c r="AE530" t="inlineStr"/>
+      <c r="AF530" t="inlineStr"/>
+      <c r="AG530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -35409,6 +41539,13 @@
       <c r="X531" t="inlineStr"/>
       <c r="Y531" t="inlineStr"/>
       <c r="Z531" t="inlineStr"/>
+      <c r="AA531" t="inlineStr"/>
+      <c r="AB531" t="inlineStr"/>
+      <c r="AC531" t="inlineStr"/>
+      <c r="AD531" t="inlineStr"/>
+      <c r="AE531" t="inlineStr"/>
+      <c r="AF531" t="inlineStr"/>
+      <c r="AG531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -35461,6 +41598,13 @@
       <c r="X532" t="inlineStr"/>
       <c r="Y532" t="inlineStr"/>
       <c r="Z532" t="inlineStr"/>
+      <c r="AA532" t="inlineStr"/>
+      <c r="AB532" t="inlineStr"/>
+      <c r="AC532" t="inlineStr"/>
+      <c r="AD532" t="inlineStr"/>
+      <c r="AE532" t="inlineStr"/>
+      <c r="AF532" t="inlineStr"/>
+      <c r="AG532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -35513,6 +41657,13 @@
       <c r="X533" t="inlineStr"/>
       <c r="Y533" t="inlineStr"/>
       <c r="Z533" t="inlineStr"/>
+      <c r="AA533" t="inlineStr"/>
+      <c r="AB533" t="inlineStr"/>
+      <c r="AC533" t="inlineStr"/>
+      <c r="AD533" t="inlineStr"/>
+      <c r="AE533" t="inlineStr"/>
+      <c r="AF533" t="inlineStr"/>
+      <c r="AG533" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
